--- a/naver-place-crawler/results_nail/중구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/중구_네일샵.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V54"/>
+  <dimension ref="A1:V123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -5474,6 +5474,6448 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>드로잉쇼</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>odshow@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>02-777-1090</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 남대문로 60</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>5</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1726036993</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1726036993</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>M네일</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>cjstkalswl0@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>02-318-2446</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 102 소공지하쇼핑센터</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>9</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>37690803</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37690803</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>손발공주</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>miri3891@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1325-1832</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로80길 13-26 1층</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="n">
+        <v>8</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1044748908</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1044748908</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>9층네일 명동점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>dmgktnqls@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1359-1372</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동10길 25-1 303호</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/9.nailstudio</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>258</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>23</v>
+      </c>
+      <c r="R58" t="n">
+        <v>281</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1681308543</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1681308543</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>hy nail&amp;brow</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>heeritnail@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로88다길 3 101호</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>11</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1075964890</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1075964890</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>라라네일</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>redpepper30@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1344-7250</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동9길 7 2층 라라네일</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lalanail_myeongdong</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>431</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1431</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1303128966</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1303128966</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>네일은</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>jisoo851208@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1470-4223</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로46길 17 이스트동(EAST) 1층</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/naileun_nail</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>4</v>
+      </c>
+      <c r="R61" t="n">
+        <v>11</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1988790934</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1988790934</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>명동수네일</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>yjh1000j@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1422-2439</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 58 회현지하쇼핑센터 바-5호</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/na.il_melody?igsh=MXdsejdoZjF6YWRzcQ==</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>3</v>
+      </c>
+      <c r="R62" t="n">
+        <v>19</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1236645309</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1236645309</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>레푸스 청계천점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>refuss_care@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1462-2414</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 청계천로 400 롯데캐슬베네치아메가몰 2층 2103호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/refuss_care</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>1053</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>953</v>
+      </c>
+      <c r="R63" t="n">
+        <v>2006</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1308679538</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1308679538</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Nail the sharp</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>happyjoint-hospital@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 32 남산타운2상가 407호</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/nail_the_sharp/</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" t="n">
+        <v>12</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1917957135</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1917957135</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>바비 네일왁싱</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>uchka247@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1490-9887</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로44길 6-9 4층</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/barbie.waxnail</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>161</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>3</v>
+      </c>
+      <c r="R65" t="n">
+        <v>164</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1019484164</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1019484164</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>아이러브네일</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>saddysad@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>02-2231-8000</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 청계천로 400</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1</v>
+      </c>
+      <c r="R66" t="n">
+        <v>11</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1532896403</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1532896403</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>코코네일</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>jjuahlee@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>02-318-6668</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 세종대로 70 덕제빌딩 302호</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>14</v>
+      </c>
+      <c r="R67" t="n">
+        <v>102</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1874418389</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1874418389</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>삼층네일</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>wang8241@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1327-8241</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 서소문로 139 동림빌딩 302</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/wang8241</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>530</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>13</v>
+      </c>
+      <c r="R68" t="n">
+        <v>543</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1894370134</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1894370134</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>네일리</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ksy3315@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1358-8653</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 세종대로20길 23 2층 206호(노모어피자,반포식스건물 아님)</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_lee____</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>9</v>
+      </c>
+      <c r="R69" t="n">
+        <v>111</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>2065943871</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2065943871</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>네일도사랑해 본점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>nesanail@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1442-9779</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동2길 57 태평양빌딩 8층</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.lovu</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>169</v>
+      </c>
+      <c r="R70" t="n">
+        <v>344</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>37294039</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37294039</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>나비네일</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>jytgh@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>02-319-7844</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동7길 19 중원빌딩 505호</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>http://instagram.com/navinailnavinail</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>2</v>
+      </c>
+      <c r="R71" t="n">
+        <v>28</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>735546684</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/735546684</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>을지네일해</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>hy0d0ng2@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1366-2991</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로 88 지하층 을특15호(구.을지네일로)</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/euljinail_hae</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>2</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>2038116522</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2038116522</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>네일인</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>jisoo851208@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1344-4179</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 46</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>1</v>
+      </c>
+      <c r="R73" t="n">
+        <v>2</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1071509328</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1071509328</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>네일리듄</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>nail_lidune@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1373-9377</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로 393-1 써니빌딩 601호</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_TURxjn</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>9</v>
+      </c>
+      <c r="R74" t="n">
+        <v>124</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1983160367</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1983160367</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>요거네일</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>daonnail0305@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1305-9862</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로74길 8 1층 요거네일</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yogu_nail</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>143</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>3</v>
+      </c>
+      <c r="R75" t="n">
+        <v>146</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1507870976</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1507870976</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>마레네일 회현지하쇼핑센터점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>skrud8631@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 58</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>3</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>37588265</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37588265</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>호시탐탐네일</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>uvistavie@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>02-6361-8521</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 남대문로 78 하나허브빌딩 1층</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>2</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>19816425</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19816425</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Nail</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>wogns2605@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로 124 명동역지하쇼핑센터</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>37587277</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37587277</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>안온네일</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>didakf032@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0507-1407-4494</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 서애로1길 11 헤센스마트상가 1층 121호 안온네일</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_zuYRG/chat</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>3</v>
+      </c>
+      <c r="R79" t="n">
+        <v>109</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>1306558328</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1306558328</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>손톱마녀</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>xxooxx0114@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>02-756-7725</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 58</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>10</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>1280944802</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1280944802</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>크리스탈손톱</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>juyean123@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>02-3398-4445</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 장충단로 275</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1</v>
+      </c>
+      <c r="R81" t="n">
+        <v>4</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>1895018257</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1895018257</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>오렌지네일 회현지하쇼핑센터점</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>skrud8631@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 58 회현지하쇼핑센터 사2</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>1</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>31315249</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31315249</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>유르네일</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>sohee5369@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로 414</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>http://instagram.com/yurr_nail</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>6</v>
+      </c>
+      <c r="R83" t="n">
+        <v>84</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>1907754185</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1907754185</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>네일드윌</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ramiu_s@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1349-8525</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 마장로18길 6 7층 701호</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_KDKmG/chat</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>2058420406</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2058420406</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>네일하트</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>nailheart053@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1484-8604</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동길 47 양원빌딩3층</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>373</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>9</v>
+      </c>
+      <c r="R85" t="n">
+        <v>382</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>1101101042</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1101101042</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>네일블룸 청구점</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>oladeoro@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>02-2231-0522</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 청구로4길 9</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>2</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>21888751</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21888751</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>비아살롱</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>by-won@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0507-1346-5958</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 114-4 MH빌딩 2층</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/by-won</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>98</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>110</v>
+      </c>
+      <c r="R87" t="n">
+        <v>208</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>1544827136</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1544827136</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>더네일인명동</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>julie6060@naver.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>02-3789-7872</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동2길 56-1</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_xiMLQj</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>220</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>859</v>
+      </c>
+      <c r="R88" t="n">
+        <v>1079</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>37224344</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37224344</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>리라뷰티</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>rira_225@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1403-3136</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로18길 6 (남산동1가) 2층 리라뷰티</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lira_4994/</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>271</v>
+      </c>
+      <c r="R89" t="n">
+        <v>392</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>1100664846</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1100664846</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>아머네일</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>hahaha__0@naver.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0507-1364-4429</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 마른내로 74 1층 아머네일</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_pzkMG</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>262</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>96</v>
+      </c>
+      <c r="R90" t="n">
+        <v>358</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>1312237193</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1312237193</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>네일멜로디</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>zadkiel80@naver.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0507-1458-7441</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 58 가-30</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/na.il_melody</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>2087273795</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2087273795</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>리오풋케어</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>rio-footcare@naver.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0507-1448-3378</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 청계천로 400 롯데캐슬배네치아 메가몰동 1층 1122호 리오풋케어</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rio-footcare</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>208</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>673</v>
+      </c>
+      <c r="R92" t="n">
+        <v>881</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>38571388</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38571388</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>굿모닝네일</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>thdgml3521@naver.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0507-1400-8607</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로 258 자산빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gmnail_eyelash</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>238</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>6</v>
+      </c>
+      <c r="R93" t="n">
+        <v>244</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>13051690</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13051690</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>가디스네일</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ara_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>arachonail@gmail.com</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0507-1396-8776</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로18길 24 3층</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@aranail</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>5</v>
+      </c>
+      <c r="R94" t="n">
+        <v>44</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>19851675</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19851675</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>네일 을지로지하쇼핑센터3구역점</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>skrud8631@naver.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>02-2278-2990</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로 131 을지로3구역지하쇼핑</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>3</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>37588249</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37588249</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>네일블라썸</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>wilklove@naver.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>0507-1347-8173</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 102 95호</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>330</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>10</v>
+      </c>
+      <c r="R96" t="n">
+        <v>340</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>1794862527</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1794862527</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>테라피 여유</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>suyom819@naver.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0507-1368-6500</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로83길 46 5층</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gridau_nailsalon</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>7</v>
+      </c>
+      <c r="R97" t="n">
+        <v>51</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>1353443114</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1353443114</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>마녀사냥 회현지하쇼핑센터점</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>geein0808@naver.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>02-777-7748</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 65-1</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>36</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>61218861</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/61218861</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>더샵 네일</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>tiger9313@naver.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0507-1305-9365</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 58 회현지하쇼핑센터 다-5호</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>2</v>
+      </c>
+      <c r="R99" t="n">
+        <v>23</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>230882348</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/230882348</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>RANSNAIL</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ransnail@naver.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 58</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>1077056709</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1077056709</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>세아현대아울렛동대문점</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>anne0504@naver.com</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 장충단로13길 20 현대아울렛동대문점B1</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>1421171519</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1421171519</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>네일퐁당</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>skan612@naver.com</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>0507-1342-2541</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 동호로7길 14 2층</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/CVh14YJhw8l/?utm_medium=copy_link</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>751</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>9</v>
+      </c>
+      <c r="R102" t="n">
+        <v>760</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>1234653779</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1234653779</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>손톱공주 회현지하쇼핑센터점</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>skrud8631@naver.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 58</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>37586344</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37586344</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>라무르네일</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>dntrlsp506@naver.com</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>02-2274-2164</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로 248 104호(묵정동)</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_TGklxj</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>3</v>
+      </c>
+      <c r="R104" t="n">
+        <v>22</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>1185961653</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1185961653</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>묘나하우스</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>hanil36chin@naver.com</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>0507-1373-9597</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>대구광역시 중구 태평로 176-7 1층 105호</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_KXxlkxj</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>4</v>
+      </c>
+      <c r="R105" t="n">
+        <v>4</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>1843844140</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1843844140</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>GK네일 현대시티아울렛 동대문점</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>liziah@naver.com</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 장충단로13길 20 지하1층</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gknaildongdaemun?igsh=MTM5OTg0OHRzdXVjZg%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>331</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>46</v>
+      </c>
+      <c r="R106" t="n">
+        <v>377</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>1245812382</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1245812382</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>꽁냥네일</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>qorgh1236@naver.com</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>0507-1418-2440</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 장충단로 249-28 3층</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ggongnyang_nail</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>274</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>40</v>
+      </c>
+      <c r="R107" t="n">
+        <v>314</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>1570914826</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1570914826</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>네일바이연</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>twinkle_gy@naver.com</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>0507-1317-9237</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소월로2길 30 남산트라팰리스 1층 108호(T타워 옆 건물)(안에있음</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>http://instagram.com/_nailby_yeon</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>389</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>5</v>
+      </c>
+      <c r="R108" t="n">
+        <v>394</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>1319851472</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1319851472</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>헤이뷰티 스튜디오</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>gemma0321@naver.com</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>0507-1404-0899</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 32 5상가동 1층 102호</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>42</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>1656356418</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1656356418</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>네일모노</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>vbrose92@naver.com</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>0507-1335-5164</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로42나길 57 101호</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_gFskxj</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>2</v>
+      </c>
+      <c r="R110" t="n">
+        <v>27</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>1174841316</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1174841316</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>강앤니네일스</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>beczzam@naver.com</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>0507-1468-2316</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 장충단로 227-2 4층</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>http://instagram.com/kangannynails</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>1</v>
+      </c>
+      <c r="R111" t="n">
+        <v>1</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>1711237836</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1711237836</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>엔79 Nail</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>tmsla_zz@naver.com</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>0507-1390-0326</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동길 36-1 삼호빌딩 7층 701호</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>163</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>19</v>
+      </c>
+      <c r="R112" t="n">
+        <v>182</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>1756267523</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1756267523</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>엘로아네일</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>hhhong88@naver.com</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>0507-1314-9339</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로 12 시청광장지하쇼핑센터(시티스타몰) 607호 엘로아 네일</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/eloa__nail/</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>8</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>2087274322</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2087274322</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>바이올렛네일</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>violet_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>02-2118-8867</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 장충단로 247 굿모닝시티 B2 6호</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" t="n">
+        <v>2</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>120895291</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/120895291</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>오프엠네일</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>hazelnutt7@naver.com</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동4길 40 4층</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>3</v>
+      </c>
+      <c r="R115" t="n">
+        <v>65</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>2099192808</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2099192808</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>지호네일</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>yongsanly@naver.com</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>0507-1314-5759</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 265 5층,6층</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jihonail</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>2</v>
+      </c>
+      <c r="R116" t="n">
+        <v>2</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>1285361463</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1285361463</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>티파니네일아트 회현지하쇼핑센터점</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>skrud8631@naver.com</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 58</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>37588405</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37588405</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>에이탑네일</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>sushigyosen@naver.com</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>0507-1372-2148</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동4길 12-1 3층</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/a.top_nail</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>249</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>66</v>
+      </c>
+      <c r="R118" t="n">
+        <v>315</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>1446197361</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1446197361</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>네일온도 약수점</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>beloved_may@naver.com</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>0507-1389-2716</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 동호로 169 2층 제1호</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailondo.yaksu</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>195</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>12</v>
+      </c>
+      <c r="R119" t="n">
+        <v>207</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>1088963203</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1088963203</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>치즈네일</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>43995@naver.com</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>02-6405-4578</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로47길 26 세원빌딩 4층 401호 치즈네일</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cheesenail</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>1</v>
+      </c>
+      <c r="R120" t="n">
+        <v>58</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>37542182</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37542182</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>트웬티네일</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>naillab20@naver.com</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>02-2233-7111</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 32 남산타운아파트 5상가(정문상가) 308호 트웬티네일</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/20nail.j_lash/</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>112</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>149</v>
+      </c>
+      <c r="R121" t="n">
+        <v>261</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>38305196</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38305196</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>케이네일</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>blueqks@naver.com</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>0507-1323-5214</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 179 2층</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>10</v>
+      </c>
+      <c r="R122" t="n">
+        <v>16</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>1614986871</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1614986871</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>프로뷰티</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>probeauty_blog@naver.com</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>0507-1435-2789</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동8가길 9 3층</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/probeauty_blog</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>557</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>670</v>
+      </c>
+      <c r="R123" t="n">
+        <v>1227</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>19997455</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19997455</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/naver-place-crawler/results_nail/중구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/중구_네일샵.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V65"/>
+  <dimension ref="A1:V122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,11 @@
           <t>읍내쌀롱</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>hot1god@naver.com</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
@@ -920,7 +924,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1018,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1108,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1202,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1292,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1307,11 @@
           <t>더나은네일</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>merryyear09@naver.com</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -1374,7 +1382,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1476,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1491,11 @@
           <t>아머네일</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>dntndus111@naver.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
@@ -1558,7 +1570,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1664,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1758,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1852,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1867,11 @@
           <t>네일블라썸</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>wilklove@naver.com</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
@@ -1930,7 +1946,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1961,11 @@
           <t>깜네일 회현지하쇼핑센터점</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>skrud8631@naver.com</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
@@ -2016,7 +2036,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2051,11 @@
           <t>Diamond Nails</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ksj673232@naver.com</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
@@ -2106,7 +2130,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2224,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2318,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2416,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2506,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2600,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2617,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>rhubarbcustard@naver.com</t>
+          <t>nail_hy-@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2666,7 +2690,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2784,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2799,11 @@
           <t>네일온도 약수점</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>beloved_may@naver.com</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
@@ -2850,7 +2878,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2972,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3066,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3156,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3250,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3265,11 @@
           <t>네일인</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>edukin_edu@naver.com</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
@@ -3312,7 +3344,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3438,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3532,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3626,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3720,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3814,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3908,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3970,7 +4002,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4096,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4190,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4280,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4374,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4357,11 +4389,7 @@
           <t>빨간고양이네일 을지로입구지하쇼핑센터점</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>skrud8631@naver.com</t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
@@ -4436,7 +4464,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4558,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4652,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4667,11 @@
           <t>M네일</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>cjstkalswl0@naver.com</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
@@ -4714,7 +4746,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4808,7 +4840,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4930,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4992,7 +5024,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5118,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5180,7 +5212,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5306,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5340,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cheesenail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5318,7 +5350,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5368,7 +5400,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5494,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5588,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5650,7 +5682,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5772,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5866,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5960,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5994,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/machojj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5972,20 +6004,24 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4xms2</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr">
         <is>
           <t>X</t>
@@ -6022,7 +6058,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6092,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sHajSJei</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6066,7 +6102,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6076,10 +6112,14 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wq9b3dr</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr">
         <is>
           <t>O</t>
@@ -6116,7 +6156,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6246,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6340,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6434,7 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6449,11 @@
           <t>손톱공주 회현지하쇼핑센터점</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>skrud8631@naver.com</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
@@ -6480,7 +6524,5289 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>지호네일</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>yongsanly@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1314-5759</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 265 5층,6층</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jihonail</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>2</v>
+      </c>
+      <c r="R66" t="n">
+        <v>2</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1285361463</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1285361463</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>레푸스 청계천점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>refuss_care@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1462-2414</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 청계천로 400 롯데캐슬베네치아메가몰 2층 2103호</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/refuss_care</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>1067</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>952</v>
+      </c>
+      <c r="R67" t="n">
+        <v>2019</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1308679538</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1308679538</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>네일바이연</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>twinkle_gy@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1317-9237</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소월로2길 30 남산트라팰리스 1층 108호(T타워 옆 건물)(안에있음</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>http://instagram.com/_nailby_yeon</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>391</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>5</v>
+      </c>
+      <c r="R68" t="n">
+        <v>396</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1319851472</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1319851472</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>네일모노</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ekgus9633@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1335-5164</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로42나길 57 101호</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_gFskxj</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>2</v>
+      </c>
+      <c r="R69" t="n">
+        <v>27</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1174841316</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1174841316</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>묘나하우스</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>hanil36chin@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1373-9597</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>대구광역시 중구 태평로 176-7 1층 105호</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>4</v>
+      </c>
+      <c r="R70" t="n">
+        <v>4</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1843844140</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1843844140</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>네일스퀘어</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>wjsthfk0625@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>02-318-4200</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 남대문로 67 롯데영플라자</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>21</v>
+      </c>
+      <c r="R71" t="n">
+        <v>35</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>21553272</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21553272</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>란스</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ypplove@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 회현동2가</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>48</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1498975945</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1498975945</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>네일드윌</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ramiu_s@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1349-8525</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 마장로18길 6 7층 701호</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>2058420406</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2058420406</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>네일블룸 청구점</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>oladeoro@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>02-2231-0522</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 청구로4길 9</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>2</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>21888751</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21888751</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>마녀사냥 회현지하쇼핑센터점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>geein0808@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>02-777-7748</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 65-1</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>36</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>61218861</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/61218861</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>트웬티네일</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>naillab20@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>02-2233-7111</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 32 남산타운아파트 5상가(정문상가) 308호 트웬티네일</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>112</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>149</v>
+      </c>
+      <c r="R76" t="n">
+        <v>261</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>38305196</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38305196</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>러빗네일</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>hyokyungsea@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0507-1340-3760</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 청파로 464 103호 러빗네일</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>151</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>7</v>
+      </c>
+      <c r="R77" t="n">
+        <v>158</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>1027224018</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1027224018</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>릴리엔젤네일</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>kiyu0987@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 남대문로 117 동아빌딩 지하1층</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4jrau</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>235</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>52</v>
+      </c>
+      <c r="R78" t="n">
+        <v>287</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>1110775717</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1110775717</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>티파니네일아트 회현지하쇼핑센터점</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>skrud8631@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 58</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>37588405</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37588405</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>리라뷰티</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>rira_225@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로18길 6 (남산동1가) 2층 리라뷰티</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lira_4994/</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>276</v>
+      </c>
+      <c r="R80" t="n">
+        <v>396</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>1100664846</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1100664846</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>네일앤제이</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>kk7775@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0507-1321-1745</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로44길 119</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xbsRxeT</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>4</v>
+      </c>
+      <c r="R81" t="n">
+        <v>69</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>1183920006</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1183920006</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>안젤라네일샵</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>angella3977@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0507-1493-3335</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 102 소공지하쇼핑센터 57호</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/angella3977</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>663</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>12</v>
+      </c>
+      <c r="R82" t="n">
+        <v>675</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>1274163754</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1274163754</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>엘로아네일</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>hhhong88@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1314-9339</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로 12 시청광장지하쇼핑센터(시티스타몰) 607호 엘로아 네일</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/eloa__nail/</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>11</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>2087274322</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2087274322</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>마녀세상</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>punkwitch@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 65-1</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>1</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>1874819639</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1874819639</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>꽁냥네일</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>qorgh1236@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1418-2440</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 장충단로 249-28 3층</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ggongnyang_nail</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>276</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>42</v>
+      </c>
+      <c r="R85" t="n">
+        <v>318</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>1570914826</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1570914826</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>네일 괜찮아</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>nobleliz_@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0507-1423-7899</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로46길 17 지하1층B102호</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_nail_ok_</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>5</v>
+      </c>
+      <c r="R86" t="n">
+        <v>14</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>1040309489</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1040309489</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>오프엠네일</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>hgy___g@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동4길 40 4층</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w9ohuf7</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>6</v>
+      </c>
+      <c r="R87" t="n">
+        <v>100</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>2099192808</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2099192808</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>네일아트재료</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>네일MOA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>02-567-5253</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 남대문시장길 37</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>http://www.nailmoa.co.kr</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>1</v>
+      </c>
+      <c r="R88" t="n">
+        <v>20</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>1179880730</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1179880730</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>삼층네일</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>wang8241@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1327-8241</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 서소문로 139 동림빌딩 302</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/wang8241</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>531</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>13</v>
+      </c>
+      <c r="R89" t="n">
+        <v>544</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>1894370134</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1894370134</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>RANSNAIL</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ransnail@naver.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 58</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>1077056709</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1077056709</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>수네일</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>qkrqhrdfrn@naver.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>02-775-1447</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 58</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>1253308517</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1253308517</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Nail the sharp</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>happyjoint-hospital@naver.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 32 남산타운2상가 407호</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/nail_the_sharp/</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>1</v>
+      </c>
+      <c r="R92" t="n">
+        <v>12</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>1917957135</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1917957135</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>케이네일</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>blueqks@naver.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0507-1323-5214</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 179 2층</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>10</v>
+      </c>
+      <c r="R93" t="n">
+        <v>16</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>1614986871</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1614986871</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>헤이뷰티 스튜디오</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>gemma0321@naver.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0507-1404-0899</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 32 5상가동 1층 102호</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>43</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>1656356418</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1656356418</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>네일스토리 소공지하쇼핑센터점</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>02-2293-2078</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 102 소공지하쇼핑센터 89</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>1</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>31315224</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31315224</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>드로잉쇼</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>odshow@naver.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>02-777-1090</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 남대문로 60</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>5</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>1726036993</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1726036993</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>꼬뇨네일</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>sstar0728@naver.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로42가길 12 2층 꼬뇨네일</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>http://instagram.com/kkonyo_nail</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>18</v>
+      </c>
+      <c r="R97" t="n">
+        <v>55</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>35563100</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35563100</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>네일하트</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>0507-1484-8604</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동길 47 양원빌딩3층</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>373</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>9</v>
+      </c>
+      <c r="R98" t="n">
+        <v>382</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>1101101042</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1101101042</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>굿모닝네일</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>clsrn9606@naver.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0507-1400-8607</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로 258 자산빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gmnail_eyelash</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>241</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>6</v>
+      </c>
+      <c r="R99" t="n">
+        <v>247</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>13051690</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13051690</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>애요네일</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>bongssang_@naver.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0507-1385-0321</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로36길 45 지하 애요네일</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_ayo_nail</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>22</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>2055335804</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2055335804</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>동감 네일</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>5nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소월로 10 단암빌딩 지하1층</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/donggam_nail</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>21</v>
+      </c>
+      <c r="R101" t="n">
+        <v>51</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>37460311</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37460311</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>더네일인명동</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>julie6060@naver.com</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>02-3789-7872</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동2길 56-1</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_xiMLQj</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>221</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>859</v>
+      </c>
+      <c r="R102" t="n">
+        <v>1080</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>37224344</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37224344</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Nail</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>wogns2605@naver.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로 124 명동역지하쇼핑센터</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>1</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>37587277</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37587277</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>정네일</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>superstarv@naver.com</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>02-363-8160</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 청파로 426 서울역롯데마트 3층</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jungnail2007</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>240</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>4</v>
+      </c>
+      <c r="R104" t="n">
+        <v>244</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>31950322</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31950322</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>9층네일 명동점</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>dmgktnqls@naver.com</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>0507-1359-1372</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동10길 25-1 303호</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/9.nailstudio</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>258</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>23</v>
+      </c>
+      <c r="R105" t="n">
+        <v>281</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>1681308543</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1681308543</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>크리스탈손톱</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>juyean123@naver.com</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>02-3398-4445</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 장충단로 275</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>1</v>
+      </c>
+      <c r="R106" t="n">
+        <v>4</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>1895018257</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1895018257</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>알렌시아네일</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>mugununa@naver.com</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>0507-1352-5127</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 동호로 172 1층 알렌시아네일</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>672</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>12</v>
+      </c>
+      <c r="R107" t="n">
+        <v>684</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>1517501228</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1517501228</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>밀리미터네일</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>zzan323@naver.com</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 청구로3길 79 1층 102호</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_eEUQxj</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>3</v>
+      </c>
+      <c r="R108" t="n">
+        <v>70</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>1846303126</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1846303126</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>라라네일</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>redpepper30@naver.com</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>0507-1344-7250</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동9길 7 2층 라라네일</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lalanail_myeongdong</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>1001</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>431</v>
+      </c>
+      <c r="R109" t="n">
+        <v>1432</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>1303128966</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1303128966</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>지아네일</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>jjaa1334@naver.com</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동10길 40 6층</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jeonjia9</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>10</v>
+      </c>
+      <c r="R110" t="n">
+        <v>75</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>1279897442</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1279897442</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>라무르네일</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>lifemelike@naver.com</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>02-2274-2164</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로 248 104호(묵정동)</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_TGklxj</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>3</v>
+      </c>
+      <c r="R111" t="n">
+        <v>22</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>1185961653</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1185961653</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>마레네일 회현지하쇼핑센터점</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>skrud8631@naver.com</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 58</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>3</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>37588265</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37588265</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>네일리</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>0507-1358-8653</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 세종대로20길 23 2층 206호(노모어피자,반포식스건물 아님)</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_lee____</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>9</v>
+      </c>
+      <c r="R113" t="n">
+        <v>119</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>2065943871</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2065943871</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>명동네일 제니뷰티</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>hyoyeol@naver.com</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>0507-1487-9603</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동8길 43 3층</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jennybeauty.md/</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" t="n">
+        <v>47</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>1845062262</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1845062262</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>오니네일</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>wjsska1907@naver.com</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>070-4798-7907</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 만리재로33길 21 리가 아파트상가 103호</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>3</v>
+      </c>
+      <c r="R115" t="n">
+        <v>120</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>37002673</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37002673</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>손톱마녀</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>xxooxx0114@naver.com</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>02-756-7725</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 58</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>10</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>1280944802</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1280944802</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>핑크레이디 회현지하쇼핑센터점</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>geein0808@naver.com</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 명동8나길 52-1</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>2</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>37588413</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37588413</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>비아살롱</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>by-won@naver.com</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>0507-1346-5958</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 114-4 MH빌딩 2층</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/by-won</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>110</v>
+      </c>
+      <c r="R118" t="n">
+        <v>209</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>1544827136</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1544827136</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>네일퐁당</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>0507-1342-2541</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 동호로7길 14 2층</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/CVh14YJhw8l/?utm_medium=copy_link</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>750</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>9</v>
+      </c>
+      <c r="R119" t="n">
+        <v>759</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>1234653779</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1234653779</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>바이올렛네일</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>violet_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>02-2118-8867</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 장충단로 247 굿모닝시티 B2 6호</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>2</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>120895291</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/120895291</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>hy nail&amp;brow</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>hy_9857@naver.com</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로88다길 3 101호</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>11</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>1075964890</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1075964890</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>네일멜로디</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>zadkiel80@naver.com</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>0507-1458-7441</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공로 58 가-30</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/na.il_melody</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>4</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>2087273795</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2087273795</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/중구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/중구_네일샵.xlsx
@@ -661,7 +661,11 @@
           <t>네일아트</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>soseum@naver.com</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
@@ -751,7 +755,11 @@
           <t>오렌지네일 회현지하쇼핑센터점</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>skrud8631@naver.com</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -837,7 +845,11 @@
           <t>네일블룸 청구점</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>oladeoro@naver.com</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
@@ -1021,7 +1033,11 @@
           <t>마레네일 회현지하쇼핑센터점</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>skrud8631@naver.com</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
@@ -1107,7 +1123,11 @@
           <t>오렌지네일</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>lgs1636@naver.com</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
@@ -1475,7 +1495,11 @@
           <t>네일하트</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>nailheart053@naver.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
@@ -1565,7 +1589,11 @@
           <t>리라뷰티</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>rira_225@naver.com</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -2113,7 +2141,11 @@
           <t>앙떼떼 네일&amp;속눈썹</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>pilnsaby100@naver.com</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
@@ -2203,7 +2235,11 @@
           <t>네일인</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>mneilacademy@naver.com</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
@@ -2481,7 +2517,11 @@
           <t>니꼬네일</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>hahere@naver.com</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
@@ -2755,7 +2795,11 @@
           <t>네일스토리 소공지하쇼핑센터점</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>skrud8631@naver.com</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
@@ -3033,7 +3077,11 @@
           <t>네일스퀘어</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>wjsthfk0625@naver.com</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
@@ -3311,7 +3359,11 @@
           <t>란스</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>devilduo@naver.com</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
@@ -3397,7 +3449,11 @@
           <t>네일 괜찮아</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>nobleliz_@naver.com</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
@@ -3487,7 +3543,11 @@
           <t>명동수네일</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>yjh1000j@naver.com</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
@@ -3634,10 +3694,10 @@
         <v>113</v>
       </c>
       <c r="Q35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R35" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3671,7 +3731,11 @@
           <t>세아현대아울렛동대문점</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>anne0504@naver.com</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
@@ -5335,7 +5399,11 @@
           <t>효녀네일</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>hy0d0ng2@naver.com</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
@@ -5515,7 +5583,11 @@
           <t>더샵 네일</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>tiger9313@naver.com</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
@@ -5605,7 +5677,11 @@
           <t>네일블라썸</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>wilklove@naver.com</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
@@ -5695,7 +5771,11 @@
           <t>꽁냥네일</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>qorgh1236@naver.com</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
@@ -5785,7 +5865,11 @@
           <t>푸딩네일</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>hero_0304@naver.com</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
@@ -5875,7 +5959,11 @@
           <t>네일앤제이</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>kk7775@naver.com</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
@@ -5965,7 +6053,11 @@
           <t>네일온도 약수점</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>beloved_may@naver.com</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
@@ -6055,7 +6147,11 @@
           <t>루아르블랑 네일</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>democratic9b1@naver.com</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
@@ -6199,13 +6295,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="Q63" t="n">
         <v>433</v>
       </c>
       <c r="R63" t="n">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6239,7 +6335,11 @@
           <t>M네일</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>cjstkalswl0@naver.com</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
@@ -6331,7 +6431,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>sstar0728@naver.com</t>
+          <t>mono1584@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -6513,7 +6613,11 @@
           <t>네일 을지로지하쇼핑센터3구역점</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>skrud8631@naver.com</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
@@ -7257,7 +7361,11 @@
           <t>테라피 여유</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>suyom819@naver.com</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
@@ -7347,7 +7455,11 @@
           <t>핑크레이디 회현지하쇼핑센터점</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>geein0808@naver.com</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
@@ -7433,7 +7545,11 @@
           <t>네일링</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>gulgomi@naver.com</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
@@ -7519,7 +7635,11 @@
           <t>드로잉쇼</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>odshow@naver.com</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
@@ -7703,7 +7823,11 @@
           <t>바이올렛네일</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>violet_nail@naver.com</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
@@ -8075,7 +8199,11 @@
           <t>RANSNAIL</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ransnail@naver.com</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
@@ -8161,7 +8289,11 @@
           <t>네일리앤래쉬</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>dear_my_spring@naver.com</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
@@ -9093,7 +9225,11 @@
           <t>마녀세상</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>punkwitch@naver.com</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
@@ -9179,7 +9315,11 @@
           <t>나비네일</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>jytgh@naver.com</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
@@ -9269,7 +9409,11 @@
           <t>크리스탈손톱</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>juyean123@naver.com</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
@@ -9641,7 +9785,11 @@
           <t>아셀네일</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>asher9809@naver.com</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
@@ -9727,7 +9875,11 @@
           <t>네일드윌</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ramiu_s@naver.com</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
@@ -9907,7 +10059,11 @@
           <t>네일바이연</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>twinkle_gy@naver.com</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
@@ -10181,7 +10337,11 @@
           <t>네일퐁당</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>skan612@naver.com</t>
+        </is>
+      </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
@@ -10231,13 +10391,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="Q107" t="n">
         <v>9</v>
       </c>
       <c r="R107" t="n">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -10455,7 +10615,11 @@
           <t>GK네일 현대시티아울렛 동대문점</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>liziah@naver.com</t>
+        </is>
+      </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
@@ -10545,7 +10709,11 @@
           <t>빨간고양이네일 을지로입구지하쇼핑센터점</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>skrud8631@naver.com</t>
+        </is>
+      </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
@@ -10635,7 +10803,11 @@
           <t>센스네일</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>nail_hy-@naver.com</t>
+        </is>
+      </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
@@ -10815,7 +10987,11 @@
           <t>알렌시아네일</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>mugununa@naver.com</t>
+        </is>
+      </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
@@ -10865,13 +11041,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="Q114" t="n">
         <v>12</v>
       </c>
       <c r="R114" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -10905,7 +11081,11 @@
           <t>9층네일 명동점</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>dmgktnqls@naver.com</t>
+        </is>
+      </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
@@ -10995,7 +11175,11 @@
           <t>네일아토</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>sk3374@naver.com</t>
+        </is>
+      </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
@@ -11330,10 +11514,10 @@
         <v>571</v>
       </c>
       <c r="Q119" t="n">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="R119" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -11461,7 +11645,11 @@
           <t>네일도사랑해 본점</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>nesanail@naver.com</t>
+        </is>
+      </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_nail/중구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/중구_네일샵.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,39 +564,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>손톱마녀</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>xxooxx0114@naver.com</t>
-        </is>
-      </c>
+          <t>밀리미터네일</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>02-756-7725</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 58</t>
+          <t>서울특별시 중구 청구로3길 79 1층 102호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_eEUQxj</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -612,22 +604,22 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +628,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1280944802</t>
+          <t>1846303126</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1280944802</t>
+          <t>https://m.place.naver.com/place/1846303126</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -658,29 +650,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>네일아트</t>
+          <t>네일아토</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>soseum@naver.com</t>
+          <t>sk3374@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>070-4257-5062</t>
+          <t>0507-1416-6630</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 58</t>
+          <t>서울특별시 중구 남대문로 29-1 3층 301호(남대문로3가)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_ato</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +682,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -711,17 +703,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>6</v>
+        <v>192</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>214</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +722,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>31315269</t>
+          <t>1446399532</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31315269</t>
+          <t>https://m.place.naver.com/place/1446399532</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -752,20 +744,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>오렌지네일 회현지하쇼핑센터점</t>
+          <t>헤이뷰티 스튜디오</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>skrud8631@naver.com</t>
+          <t>gemma0321@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1404-0899</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 58 회현지하쇼핑센터 사2</t>
+          <t>서울특별시 중구 다산로 32 5상가동 1층 102호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -805,13 +801,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +816,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>31315249</t>
+          <t>1656356418</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31315249</t>
+          <t>https://m.place.naver.com/place/1656356418</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -842,29 +838,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일블룸 청구점</t>
+          <t>라라네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>oladeoro@naver.com</t>
+          <t>redpepper30@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02-2231-0522</t>
+          <t>0507-1344-7250</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 중구 청구로4길 9</t>
+          <t>서울특별시 중구 명동9길 7 2층 라라네일</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lalanail_myeongdong</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -874,7 +870,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -895,17 +891,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1003</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>433</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>1436</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,17 +910,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>21888751</t>
+          <t>1303128966</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21888751</t>
+          <t>https://m.place.naver.com/place/1303128966</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -936,29 +932,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Diamond Nails</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ksj673232@naver.com</t>
-        </is>
-      </c>
+          <t>효녀네일</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1420-1393</t>
+          <t>0507-1366-2991</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 중구 마른내로 155 1동 102호</t>
+          <t>서울특별시 중구 을지로 88 지하층 을특15호(구.을지네일로)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/diamondnails_korea?igsh=M2JodDNoaGtnOGdi</t>
+          <t>https://www.instagram.com/hyonyeo_nail</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,13 +985,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1000,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2040524360</t>
+          <t>2038116522</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040524360</t>
+          <t>https://m.place.naver.com/place/2038116522</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1022,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>마레네일 회현지하쇼핑센터점</t>
+          <t>세아현대아울렛동대문점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>skrud8631@naver.com</t>
+          <t>anne0504@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1043,7 +1035,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 58</t>
+          <t>서울특별시 중구 장충단로13길 20 현대아울렛동대문점B1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1083,13 +1075,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,17 +1090,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>37588265</t>
+          <t>1421171519</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37588265</t>
+          <t>https://m.place.naver.com/place/1421171519</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1120,24 +1112,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>오렌지네일</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>lgs1636@naver.com</t>
-        </is>
-      </c>
+          <t>오프엠네일</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>02-777-7476</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 35 남산 롯데캐슬</t>
+          <t>서울특별시 중구 명동4길 40 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1177,13 +1161,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>47</v>
+        <v>109</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,17 +1176,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>457971165</t>
+          <t>2099192808</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/457971165</t>
+          <t>https://m.place.naver.com/place/2099192808</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1214,25 +1198,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>동감 네일</t>
+          <t>GK네일 현대시티아울렛 동대문점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5nail@naver.com</t>
+          <t>liziah@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1339-5357</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소월로 10 단암빌딩 지하1층</t>
+          <t>서울특별시 중구 장충단로13길 20 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/donggam_nail</t>
+          <t>https://www.instagram.com/gknaildongdaemun?igsh=MTM5OTg0OHRzdXVjZg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1267,13 +1255,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>30</v>
+        <v>333</v>
       </c>
       <c r="Q9" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="R9" t="n">
-        <v>51</v>
+        <v>379</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1282,56 +1270,52 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>37460311</t>
+          <t>1245812382</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37460311</t>
+          <t>https://m.place.naver.com/place/1245812382</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>네일아트,네일샵</t>
+          <t>네일아트재료</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>더네일인명동</t>
+          <t>77에밀리</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>julie6060@naver.com</t>
+          <t>nobbob@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>02-3789-7872</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동2길 56-1</t>
+          <t>서울특별시 중구 명동4길 6 1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xiMLQj</t>
+          <t>https://www.instagram.com/emily.s_nail</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1352,7 +1336,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1361,13 +1345,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>221</v>
+        <v>12</v>
       </c>
       <c r="Q10" t="n">
-        <v>859</v>
+        <v>141</v>
       </c>
       <c r="R10" t="n">
-        <v>1080</v>
+        <v>153</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1376,17 +1360,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>37224344</t>
+          <t>1224871762</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37224344</t>
+          <t>https://m.place.naver.com/place/1224871762</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1398,34 +1382,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>안온네일</t>
+          <t>네일바이안</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>es111222@naver.com</t>
+          <t>ye1yang@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1407-4494</t>
+          <t>02-511-5621</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 중구 서애로1길 11 헤센스마트상가 1층 121호 안온네일</t>
+          <t>서울특별시 중구 남대문로9길 12 8층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_zuYRG/chat</t>
+          <t>https://www.instagram.com/nailbyahn</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1446,7 +1430,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1455,13 +1439,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="R11" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1470,17 +1454,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1306558328</t>
+          <t>1084164588</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1306558328</t>
+          <t>https://m.place.naver.com/place/1084164588</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1492,29 +1476,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>네일하트</t>
+          <t>요거네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nailheart053@naver.com</t>
+          <t>mneilacademy@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1484-8604</t>
+          <t>0507-1305-9862</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동길 47 양원빌딩3층</t>
+          <t>서울특별시 중구 퇴계로74길 8 1층 요거네일</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/yogu_nail</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1524,7 +1508,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1545,17 +1529,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>373</v>
+        <v>144</v>
       </c>
       <c r="Q12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>382</v>
+        <v>146</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1564,17 +1548,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1101101042</t>
+          <t>1507870976</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1101101042</t>
+          <t>https://m.place.naver.com/place/1507870976</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1586,25 +1570,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>리라뷰티</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>rira_225@naver.com</t>
-        </is>
-      </c>
+          <t>애요네일</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1385-0321</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로18길 6 (남산동1가) 2층 리라뷰티</t>
+          <t>서울특별시 중구 다산로36길 45 지하 애요네일</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lira_4994/</t>
+          <t>https://www.instagram.com/_ayo_nail</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1639,13 +1623,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>122</v>
+        <v>23</v>
       </c>
       <c r="Q13" t="n">
-        <v>277</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>399</v>
+        <v>23</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1654,17 +1638,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1100664846</t>
+          <t>2055335804</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1100664846</t>
+          <t>https://m.place.naver.com/place/2055335804</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1676,25 +1660,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>지아네일</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>jjaa1334@naver.com</t>
-        </is>
-      </c>
+          <t>수네일</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>02-775-1447</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동10길 40 6층</t>
+          <t>서울특별시 중구 소공로 58</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jeonjia9</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1704,7 +1688,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1725,17 +1709,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="Q14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1744,17 +1728,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1279897442</t>
+          <t>1253308517</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1279897442</t>
+          <t>https://m.place.naver.com/place/1253308517</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1766,29 +1750,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>요거네일</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>mneilacademy@naver.com</t>
-        </is>
-      </c>
+          <t>네일스퀘어</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1305-9862</t>
+          <t>02-318-4200</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로74길 8 1층 요거네일</t>
+          <t>서울특별시 중구 남대문로 67 롯데영플라자</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yogu_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1798,7 +1778,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1819,17 +1799,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>144</v>
+        <v>14</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="R15" t="n">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1838,17 +1818,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1507870976</t>
+          <t>21553272</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1507870976</t>
+          <t>https://m.place.naver.com/place/21553272</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1860,25 +1840,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>오프엠네일</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>hgy___g@naver.com</t>
-        </is>
-      </c>
+          <t>읍내쌀롱</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1332-6517</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동4길 40 4층</t>
+          <t>대구광역시 중구 태평로 176-7 102호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/eupnae_nail</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1888,7 +1868,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1909,17 +1889,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="Q16" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="R16" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1928,17 +1908,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2099192808</t>
+          <t>1400699570</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2099192808</t>
+          <t>https://m.place.naver.com/place/1400699570</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1950,29 +1930,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>애요네일</t>
+          <t>치즈네일</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>catisgod@naver.com</t>
+          <t>43995@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1385-0321</t>
+          <t>02-6405-4578</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로36길 45 지하 애요네일</t>
+          <t>서울특별시 중구 다산로47길 26 세원빌딩 4층 401호 치즈네일</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_ayo_nail</t>
+          <t>https://www.instagram.com/cheesenail</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2007,13 +1987,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2022,17 +2002,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2055335804</t>
+          <t>37542182</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055335804</t>
+          <t>https://m.place.naver.com/place/37542182</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2044,29 +2024,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>바비 네일왁싱</t>
+          <t>손톱마녀</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>uchka247@naver.com</t>
+          <t>xxooxx0114@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1490-9887</t>
+          <t>02-756-7725</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로44길 6-9 4층</t>
+          <t>서울특별시 중구 소공로 58</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/barbie.waxnail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2076,7 +2056,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2097,17 +2077,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>159</v>
+        <v>10</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>162</v>
+        <v>10</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2116,17 +2096,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1019484164</t>
+          <t>1280944802</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1019484164</t>
+          <t>https://m.place.naver.com/place/1280944802</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2138,29 +2118,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>앙떼떼 네일&amp;속눈썹</t>
+          <t>아이러브네일</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>pilnsaby100@naver.com</t>
+          <t>saddysad@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1366-0401</t>
+          <t>02-2231-8000</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>서울특별시 중구 만리재로 175 서울역센트럴자이상가 114동 대로변 1층</t>
+          <t>서울특별시 중구 청계천로 400</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_entete/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2170,7 +2150,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2191,17 +2171,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>286</v>
+        <v>10</v>
       </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>293</v>
+        <v>11</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2210,17 +2190,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1737868225</t>
+          <t>1532896403</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1737868225</t>
+          <t>https://m.place.naver.com/place/1532896403</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2232,29 +2212,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>네일인</t>
+          <t>지유네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mneilacademy@naver.com</t>
+          <t>jiyunail@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1344-4179</t>
+          <t>0507-1426-4142</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 46</t>
+          <t>서울특별시 중구 동호로10길 30 동아약수하이츠아파트상가 1층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/jiyunail</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2264,12 +2244,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2285,17 +2265,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>495</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>589</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2304,17 +2284,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1071509328</t>
+          <t>31234315</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1071509328</t>
+          <t>https://m.place.naver.com/place/31234315</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2326,29 +2306,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>맥스네일</t>
+          <t>케이네일</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>machojj@naver.com</t>
+          <t>blueqks@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>02-2272-4141</t>
+          <t>0507-1323-5214</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 204 3층</t>
+          <t>서울특별시 중구 다산로 179 2층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/machojj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2358,12 +2338,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2379,17 +2359,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>198</v>
+        <v>6</v>
       </c>
       <c r="Q21" t="n">
-        <v>532</v>
+        <v>10</v>
       </c>
       <c r="R21" t="n">
-        <v>730</v>
+        <v>16</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2398,17 +2378,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>32786203</t>
+          <t>1614986871</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32786203</t>
+          <t>https://m.place.naver.com/place/1614986871</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2420,34 +2400,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>아머네일</t>
+          <t>엘로아네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dntndus111@naver.com</t>
+          <t>hhhong88@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1364-4429</t>
+          <t>0507-1314-9339</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>서울특별시 중구 마른내로 74 1층 아머네일</t>
+          <t>서울특별시 중구 을지로 12 시청광장지하쇼핑센터(시티스타몰) 607호 엘로아 네일</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_pzkMG</t>
+          <t>https://www.instagram.com/eloa__nail/</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2468,7 +2448,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2477,13 +2457,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>262</v>
+        <v>13</v>
       </c>
       <c r="Q22" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>359</v>
+        <v>13</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2492,17 +2472,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1312237193</t>
+          <t>2087274322</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1312237193</t>
+          <t>https://m.place.naver.com/place/2087274322</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2514,12 +2494,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>니꼬네일</t>
+          <t>핑크레이디 회현지하쇼핑센터점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>hahere@naver.com</t>
+          <t>geein0808@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2527,12 +2507,12 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>서울특별시 중구 동호로10길 16 1층 102호</t>
+          <t>서울특별시 중구 명동8나길 52-1</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_nikko</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2542,7 +2522,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2563,17 +2543,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>243</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>243</v>
+        <v>2</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2582,17 +2562,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1827341634</t>
+          <t>37588413</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1827341634</t>
+          <t>https://m.place.naver.com/place/37588413</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2604,29 +2584,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>지호네일</t>
+          <t>Nail</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>suk2time@naver.com</t>
+          <t>wogns2605@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0507-1314-5759</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로 265 5층,6층</t>
+          <t>서울특별시 중구 퇴계로 124 명동역지하쇼핑센터</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jihonail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2636,7 +2612,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2657,17 +2633,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>2</v>
-      </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2676,17 +2652,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1285361463</t>
+          <t>37587277</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1285361463</t>
+          <t>https://m.place.naver.com/place/37587277</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2698,29 +2674,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>정네일</t>
+          <t>히비네일</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>susie9501@naver.com</t>
+          <t>hyok_s2@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>02-363-8160</t>
+          <t>0507-1447-2723</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>서울특별시 중구 청파로 426 서울역롯데마트 3층</t>
+          <t>서울특별시 중구 다산로42길 12 1층 102호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jungnail2007</t>
+          <t>https://www.instagram.com/hibinail_?igsh=MTVrb2l2MWQ0dXphNw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2755,13 +2731,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>244</v>
+        <v>2</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2770,17 +2746,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>31950322</t>
+          <t>2096886093</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31950322</t>
+          <t>https://m.place.naver.com/place/2096886093</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2792,24 +2768,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>네일스토리 소공지하쇼핑센터점</t>
+          <t>마녀세상</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>skrud8631@naver.com</t>
+          <t>punkwitch@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>02-2293-2078</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 102 소공지하쇼핑센터 89</t>
+          <t>서울특별시 중구 소공로 65-1</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2849,13 +2821,13 @@
         </is>
       </c>
       <c r="P26" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2864,17 +2836,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>31315224</t>
+          <t>1874819639</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31315224</t>
+          <t>https://m.place.naver.com/place/1874819639</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2886,29 +2858,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>케이네일</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>blueqks@naver.com</t>
-        </is>
-      </c>
+          <t>루아르블랑 네일</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1323-5214</t>
+          <t>0507-1483-9411</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로 179 2층</t>
+          <t>서울특별시 중구 퇴계로 293 호텔더디자이너스 DDP점 1층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/sHajSJei</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2918,7 +2886,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2934,22 +2902,22 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>6</v>
+        <v>182</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="R27" t="n">
-        <v>16</v>
+        <v>246</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2958,17 +2926,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1614986871</t>
+          <t>2013893243</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1614986871</t>
+          <t>https://m.place.naver.com/place/2013893243</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2980,39 +2948,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일모노</t>
+          <t>아셀네일</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ekgus9633@naver.com</t>
+          <t>asher9809@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0507-1335-5164</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로42나길 57 101호</t>
+          <t>서울특별시 중구 장충단로 253 10층 11호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_gFskxj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3028,22 +2992,22 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3052,17 +3016,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1174841316</t>
+          <t>1229434440</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1174841316</t>
+          <t>https://m.place.naver.com/place/1229434440</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3074,24 +3038,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>네일스퀘어</t>
+          <t>엔79 Nail</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>wjsthfk0625@naver.com</t>
+          <t>loveucream@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>02-318-4200</t>
+          <t>0507-1390-0326</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 67 롯데영플라자</t>
+          <t>서울특별시 중구 명동길 36-1 삼호빌딩 7층 701호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3131,13 +3095,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>14</v>
+        <v>163</v>
       </c>
       <c r="Q29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R29" t="n">
-        <v>35</v>
+        <v>182</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3146,17 +3110,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>21553272</t>
+          <t>1756267523</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21553272</t>
+          <t>https://m.place.naver.com/place/1756267523</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3168,34 +3132,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>충무로 하트비트 네일스튜디오</t>
+          <t>묘나하우스</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>eunishero@naver.com</t>
+          <t>hanil36chin@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1310-9697</t>
+          <t>0507-1373-9597</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>서울특별시 중구 마른내로6길 38 2층</t>
+          <t>대구광역시 중구 태평로 176-7 1층 105호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/heartbeatnailstudio</t>
+          <t>http://pf.kakao.com/_KXxlkxj</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3216,7 +3180,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3228,10 +3192,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3240,17 +3204,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2098893814</t>
+          <t>1843844140</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2098893814</t>
+          <t>https://m.place.naver.com/place/1843844140</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3262,29 +3226,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>네일멜로디</t>
+          <t>앙떼떼 네일&amp;속눈썹</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>zadkiel80@naver.com</t>
+          <t>pilnsaby100@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1458-7441</t>
+          <t>0507-1366-0401</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 58 가-30</t>
+          <t>서울특별시 중구 만리재로 175 서울역센트럴자이상가 114동 대로변 1층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/na.il_melody</t>
+          <t>https://www.instagram.com/nail_entete/</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3319,13 +3283,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>287</v>
       </c>
       <c r="Q31" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R31" t="n">
-        <v>4</v>
+        <v>294</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3334,17 +3298,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2087273795</t>
+          <t>1737868225</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2087273795</t>
+          <t>https://m.place.naver.com/place/1737868225</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3356,25 +3320,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>란스</t>
+          <t>네일온 명동본점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>devilduo@naver.com</t>
+          <t>nailon_myeongdong@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1302-8995</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>서울특별시 중구 회현동2가</t>
+          <t>서울특별시 중구 을지로 88 을특8호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nailon_myeongdong</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3384,12 +3352,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3405,17 +3373,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R32" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3424,17 +3392,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1498975945</t>
+          <t>2054691209</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1498975945</t>
+          <t>https://m.place.naver.com/place/2054691209</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3446,34 +3414,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>네일 괜찮아</t>
+          <t>더네일인명동</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>nobleliz_@naver.com</t>
+          <t>julie6060@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1423-7899</t>
+          <t>02-3789-7872</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로46길 17 지하1층B102호</t>
+          <t>서울특별시 중구 명동2길 56-1</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nail_ok_</t>
+          <t>https://pf.kakao.com/_xiMLQj</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3494,7 +3462,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3503,13 +3471,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>9</v>
+        <v>221</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>859</v>
       </c>
       <c r="R33" t="n">
-        <v>14</v>
+        <v>1080</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3518,17 +3486,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1040309489</t>
+          <t>37224344</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040309489</t>
+          <t>https://m.place.naver.com/place/37224344</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3543,11 +3511,7 @@
           <t>명동수네일</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>yjh1000j@naver.com</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
@@ -3622,7 +3586,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3634,29 +3598,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>네일리</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>ysbfly@naver.com</t>
-        </is>
-      </c>
+          <t>네일온도 약수점</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1358-8653</t>
+          <t>0507-1389-2716</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로20길 23 2층 206호(노모어피자,반포식스건물 아님)</t>
+          <t>서울특별시 중구 동호로 169 2층 제1호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_lee____</t>
+          <t>https://www.instagram.com/nailondo.yaksu</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3691,13 +3651,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>113</v>
+        <v>200</v>
       </c>
       <c r="Q35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R35" t="n">
-        <v>124</v>
+        <v>212</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3706,17 +3666,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2065943871</t>
+          <t>1088963203</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2065943871</t>
+          <t>https://m.place.naver.com/place/1088963203</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3728,20 +3688,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>세아현대아울렛동대문점</t>
+          <t>네일 을지로지하쇼핑센터3구역점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>anne0504@naver.com</t>
+          <t>skrud8631@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>02-2278-2990</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로13길 20 현대아울렛동대문점B1</t>
+          <t>서울특별시 중구 을지로 131 을지로3구역지하쇼핑</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3781,13 +3745,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3796,17 +3760,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1421171519</t>
+          <t>37588249</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1421171519</t>
+          <t>https://m.place.naver.com/place/37588249</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3818,29 +3782,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>손발공주</t>
+          <t>명동네일 제니뷰티</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>miri3891@naver.com</t>
+          <t>hyoyeol@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1325-1832</t>
+          <t>0507-1487-9603</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로80길 13-26 1층</t>
+          <t>서울특별시 중구 명동8길 43 3층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jennybeauty.md/</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3850,7 +3814,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3871,17 +3835,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3890,17 +3854,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1044748908</t>
+          <t>1845062262</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1044748908</t>
+          <t>https://m.place.naver.com/place/1845062262</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3912,29 +3876,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>비아살롱</t>
+          <t>티파니네일아트 회현지하쇼핑센터점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>by-won@naver.com</t>
+          <t>skrud8631@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0507-1346-5958</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로 114-4 MH빌딩 2층</t>
+          <t>서울특별시 중구 소공로 58</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/by-won</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3944,12 +3904,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3965,17 +3925,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3984,17 +3944,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1544827136</t>
+          <t>37588405</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1544827136</t>
+          <t>https://m.place.naver.com/place/37588405</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4006,29 +3966,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>네일하지호</t>
+          <t>오렌지네일 회현지하쇼핑센터점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>uji888@naver.com</t>
+          <t>skrud8631@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0507-1359-8728</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>서울특별시 중구 동호로10길 21 광영빌딩 402호</t>
+          <t>서울특별시 중구 소공로 58 회현지하쇼핑센터 사2</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/Nailhajiho</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4038,7 +3994,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4059,17 +4015,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>464</v>
+        <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>472</v>
+        <v>1</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4078,17 +4034,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1876886104</t>
+          <t>31315249</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1876886104</t>
+          <t>https://m.place.naver.com/place/31315249</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4100,29 +4056,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>히비네일</t>
+          <t>Diamond Nails</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>entks1020@naver.com</t>
+          <t>ksj673232@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1447-2723</t>
+          <t>0507-1420-1393</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로42길 12 1층 102호</t>
+          <t>서울특별시 중구 마른내로 155 1동 102호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hibinail_?igsh=MTVrb2l2MWQ0dXphNw%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/diamondnails_korea?igsh=M2JodDNoaGtnOGdi</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4160,10 +4116,10 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4172,17 +4128,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2096886093</t>
+          <t>2040524360</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2096886093</t>
+          <t>https://m.place.naver.com/place/2040524360</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4194,25 +4150,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nail the sharp</t>
+          <t>빨간고양이네일 을지로입구지하쇼핑센터점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>happyjoint-hospital@naver.com</t>
+          <t>skrud8631@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>02-756-4143</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로 32 남산타운2상가 407호</t>
+          <t>서울특별시 중구 을지로 58 을지로입구지하쇼핑센터 8</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_the_sharp/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4222,7 +4182,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4243,17 +4203,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4262,17 +4222,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1917957135</t>
+          <t>31315234</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1917957135</t>
+          <t>https://m.place.naver.com/place/31315234</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4244,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>깜네일 회현지하쇼핑센터점</t>
+          <t>네일스토리 소공지하쇼핑센터점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4293,11 +4253,15 @@
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>02-2293-2078</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동8나길 52-1</t>
+          <t>서울특별시 중구 소공로 102 소공지하쇼핑센터 89</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4337,13 +4301,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4352,17 +4316,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>61704046</t>
+          <t>31315224</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/61704046</t>
+          <t>https://m.place.naver.com/place/31315224</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4374,29 +4338,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>메이드인네일</t>
+          <t>비아살롱</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>madeinnail4241@naver.com</t>
+          <t>by-won@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1412-4241</t>
+          <t>0507-1346-5958</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>서울특별시 중구 동호로11길 7 녹원빌딩 1층 3호 네일샵</t>
+          <t>서울특별시 중구 다산로 114-4 MH빌딩 2층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/madeinnail4241</t>
+          <t>https://blog.naver.com/by-won</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4431,13 +4395,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="Q43" t="n">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="R43" t="n">
-        <v>139</v>
+        <v>209</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4446,17 +4410,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>38501356</t>
+          <t>1544827136</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38501356</t>
+          <t>https://m.place.naver.com/place/1544827136</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4468,29 +4432,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>에이탑네일</t>
+          <t>생크추어리 미호즈네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>adw1223@naver.com</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0507-1372-2148</t>
-        </is>
-      </c>
+          <t>stmhu27@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ncontact.roamusic.yt@gmail.com</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동4길 12-1 3층</t>
+          <t>서울특별시 중구 삼일대로 299 이화빌딩 별관</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/a.top_nail</t>
+          <t>https://www.youtube.com/channel/UCyzO0wKjVEHw9LMt3ud5Jqw</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4525,13 +4489,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>260</v>
+        <v>42</v>
       </c>
       <c r="Q44" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>328</v>
+        <v>43</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4540,17 +4504,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1446197361</t>
+          <t>1692160158</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446197361</t>
+          <t>https://m.place.naver.com/place/1692160158</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4562,25 +4526,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nail</t>
+          <t>9층네일 명동점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>wogns2605@naver.com</t>
+          <t>dmgktnqls@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1359-1372</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 124 명동역지하쇼핑센터</t>
+          <t>서울특별시 중구 명동10길 25-1 303호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/9.nailstudio</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4590,7 +4558,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4611,17 +4579,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1</v>
+        <v>259</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>282</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4630,17 +4598,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>37587277</t>
+          <t>1681308543</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37587277</t>
+          <t>https://m.place.naver.com/place/1681308543</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4652,29 +4620,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>네일은</t>
+          <t>M네일</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>sungunara226@naver.com</t>
+          <t>cjstkalswl0@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1470-4223</t>
+          <t>02-318-2446</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로46길 17 이스트동(EAST) 1층</t>
+          <t>서울특별시 중구 소공로 102 소공지하쇼핑센터</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naileun_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4684,7 +4652,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4705,17 +4673,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4724,17 +4692,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1988790934</t>
+          <t>37690803</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1988790934</t>
+          <t>https://m.place.naver.com/place/37690803</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4746,29 +4714,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>안젤라네일샵</t>
+          <t>트웬티네일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>angella3977@naver.com</t>
+          <t>naillab20@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1493-3335</t>
+          <t>02-2233-7111</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 102 소공지하쇼핑센터 57호</t>
+          <t>서울특별시 중구 다산로 32 남산타운아파트 5상가(정문상가) 308호 트웬티네일</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/angella3977</t>
+          <t>https://www.instagram.com/20nail.j_lash/</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4783,7 +4751,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4803,13 +4771,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>664</v>
+        <v>114</v>
       </c>
       <c r="Q47" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="R47" t="n">
-        <v>676</v>
+        <v>264</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4818,17 +4786,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1274163754</t>
+          <t>38305196</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1274163754</t>
+          <t>https://m.place.naver.com/place/38305196</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4840,34 +4808,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>트웬티네일</t>
+          <t>네일리듄</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>naillab20@naver.com</t>
+          <t>nail_lidune@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>02-2233-7111</t>
+          <t>0507-1373-9377</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로 32 남산타운아파트 5상가(정문상가) 308호 트웬티네일</t>
+          <t>서울특별시 중구 퇴계로 393-1 써니빌딩 601호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/20nail.j_lash/</t>
+          <t>http://pf.kakao.com/_TURxjn</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4888,7 +4856,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4897,13 +4865,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q48" t="n">
-        <v>149</v>
+        <v>9</v>
       </c>
       <c r="R48" t="n">
-        <v>262</v>
+        <v>124</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4912,17 +4880,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>38305196</t>
+          <t>1983160367</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38305196</t>
+          <t>https://m.place.naver.com/place/1983160367</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4934,25 +4902,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>티파니네일아트 회현지하쇼핑센터점</t>
+          <t>테리네일</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>skrud8631@naver.com</t>
+          <t>terrywinner@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1400-7242</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 58</t>
+          <t>서울특별시 중구 서소문로9길 28 덕수궁 롯데캐슬 상가 201동 130호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/terrywinner</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4962,12 +4934,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4983,17 +4955,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5002,17 +4974,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>37588405</t>
+          <t>31519898</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37588405</t>
+          <t>https://m.place.naver.com/place/31519898</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5024,25 +4996,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>hy nail&amp;brow</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>heeritnail@naver.com</t>
-        </is>
-      </c>
+          <t>에이탑네일</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1372-2148</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로88다길 3 101호</t>
+          <t>서울특별시 중구 명동4길 12-1 3층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/a.top_nail</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5052,7 +5024,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5073,17 +5045,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>11</v>
+        <v>259</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="R50" t="n">
-        <v>11</v>
+        <v>327</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5092,17 +5064,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1075964890</t>
+          <t>1446197361</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1075964890</t>
+          <t>https://m.place.naver.com/place/1446197361</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5114,33 +5086,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>가디스네일</t>
+          <t>디디 네일바</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ara_nail@naver.com</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>arachonail@gmail.com</t>
-        </is>
-      </c>
+          <t>heeja090@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1396-8776</t>
+          <t>0507-1476-0228</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로18길 24 3층</t>
+          <t>서울특별시 중구 을지로16길 5-5 유일빌딩4층 503호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://youtube.com/@aranail</t>
+          <t>https://www.instagram.com/didi___nailbar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5166,7 +5134,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5175,13 +5143,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>39</v>
+        <v>189</v>
       </c>
       <c r="Q51" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="R51" t="n">
-        <v>44</v>
+        <v>213</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5190,17 +5158,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>19851675</t>
+          <t>1134899134</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19851675</t>
+          <t>https://m.place.naver.com/place/1134899134</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5212,29 +5180,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>치즈네일</t>
+          <t>삼층네일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>43995@naver.com</t>
+          <t>wang8241@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>02-6405-4578</t>
+          <t>0507-1327-8241</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로47길 26 세원빌딩 4층 401호 치즈네일</t>
+          <t>서울특별시 중구 서소문로 139 동림빌딩 302</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cheesenail</t>
+          <t>https://blog.naver.com/wang8241</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5249,7 +5217,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5265,17 +5233,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>57</v>
+        <v>536</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R52" t="n">
-        <v>58</v>
+        <v>549</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5284,52 +5252,52 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>37542182</t>
+          <t>1894370134</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37542182</t>
+          <t>https://m.place.naver.com/place/1894370134</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>네일아트재료</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>77에밀리</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>nobbob@naver.com</t>
-        </is>
-      </c>
+          <t>네일앤제이</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1321-1745</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동4길 6 1층</t>
+          <t>서울특별시 중구 다산로44길 119</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/emily.s_nail</t>
+          <t>http://pf.kakao.com/_xbsRxeT</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5350,7 +5318,7 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5359,13 +5327,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="Q53" t="n">
-        <v>141</v>
+        <v>4</v>
       </c>
       <c r="R53" t="n">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5374,17 +5342,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1224871762</t>
+          <t>1183920006</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1224871762</t>
+          <t>https://m.place.naver.com/place/1183920006</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5396,29 +5364,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>효녀네일</t>
+          <t>센스네일</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>hy0d0ng2@naver.com</t>
+          <t>nail_hy-@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0507-1366-2991</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 88 지하층 을특15호(구.을지네일로)</t>
+          <t>서울특별시 중구 청계천로 400 롯데캐슬베네치아메가몰 1007호 1층 센스네일</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hyonyeo_nail</t>
+          <t>http://instagram.com/sense.nail</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5453,13 +5417,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>283</v>
       </c>
       <c r="R54" t="n">
-        <v>4</v>
+        <v>303</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5468,17 +5432,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2038116522</t>
+          <t>185384764</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038116522</t>
+          <t>https://m.place.naver.com/place/185384764</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5490,25 +5454,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>릴리엔젤네일</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>kiyu0987@naver.com</t>
-        </is>
-      </c>
+          <t>네일아트</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>070-4257-5062</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 117 동아빌딩 지하1층</t>
+          <t>서울특별시 중구 소공로 58</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://instagram.com/lilyangel_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5518,7 +5482,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5539,17 +5503,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>235</v>
+        <v>6</v>
       </c>
       <c r="Q55" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>287</v>
+        <v>6</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5558,17 +5522,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1110775717</t>
+          <t>31315269</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1110775717</t>
+          <t>https://m.place.naver.com/place/31315269</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5580,24 +5544,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>더샵 네일</t>
+          <t>hy nail&amp;brow</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>tiger9313@naver.com</t>
+          <t>heeritnail@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0507-1305-9365</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 58 회현지하쇼핑센터 다-5호</t>
+          <t>서울특별시 중구 퇴계로88다길 3 101호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5637,13 +5597,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="Q56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5652,17 +5612,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>230882348</t>
+          <t>1075964890</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/230882348</t>
+          <t>https://m.place.naver.com/place/1075964890</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5674,29 +5634,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>네일블라썸</t>
+          <t>네일하지호</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>wilklove@naver.com</t>
+          <t>kururuda@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1347-8173</t>
+          <t>0507-1359-8728</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 102 95호</t>
+          <t>서울특별시 중구 동호로10길 21 광영빌딩 402호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/Nailhajiho</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5706,7 +5666,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5727,17 +5687,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>333</v>
+        <v>464</v>
       </c>
       <c r="Q57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R57" t="n">
-        <v>343</v>
+        <v>472</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5746,17 +5706,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1794862527</t>
+          <t>1876886104</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1794862527</t>
+          <t>https://m.place.naver.com/place/1876886104</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5768,29 +5728,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>꽁냥네일</t>
+          <t>정네일</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>qorgh1236@naver.com</t>
+          <t>susie9501@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1418-2440</t>
+          <t>02-363-8160</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 249-28 3층</t>
+          <t>서울특별시 중구 청파로 426 서울역롯데마트 3층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ggongnyang_nail</t>
+          <t>https://www.instagram.com/jungnail2007</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5825,13 +5785,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>277</v>
+        <v>241</v>
       </c>
       <c r="Q58" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="R58" t="n">
-        <v>319</v>
+        <v>245</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5840,17 +5800,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1570914826</t>
+          <t>31950322</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1570914826</t>
+          <t>https://m.place.naver.com/place/31950322</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5862,24 +5822,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>푸딩네일</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>hero_0304@naver.com</t>
-        </is>
-      </c>
+          <t>오렌지네일</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>02-2233-2202</t>
+          <t>02-777-7476</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로 32 남산타운스포츠상가 103호</t>
+          <t>서울특별시 중구 소공로 35 남산 롯데캐슬</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5919,13 +5875,13 @@
         </is>
       </c>
       <c r="P59" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q59" t="n">
         <v>1</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5934,17 +5890,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1937114523</t>
+          <t>457971165</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1937114523</t>
+          <t>https://m.place.naver.com/place/457971165</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5956,39 +5912,35 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>네일앤제이</t>
+          <t>네일링</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>kk7775@naver.com</t>
+          <t>gulgomi@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0507-1321-1745</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로44길 119</t>
+          <t>서울특별시 중구 다산로 32 남산타운2상가 106호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xbsRxeT</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6004,22 +5956,22 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="Q60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R60" t="n">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6028,17 +5980,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1183920006</t>
+          <t>1720718118</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1183920006</t>
+          <t>https://m.place.naver.com/place/1720718118</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6050,29 +6002,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일온도 약수점</t>
+          <t>네일프렌즈</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>beloved_may@naver.com</t>
+          <t>friends41@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1389-2716</t>
+          <t>02-753-4179</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>서울특별시 중구 동호로 169 2층 제1호</t>
+          <t>서울특별시 중구 퇴계로 103</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailondo.yaksu</t>
+          <t>https://blog.naver.com/friends41</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6087,7 +6039,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6103,17 +6055,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="R61" t="n">
-        <v>212</v>
+        <v>10</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6122,17 +6074,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1088963203</t>
+          <t>36434848</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088963203</t>
+          <t>https://m.place.naver.com/place/36434848</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6144,29 +6096,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>루아르블랑 네일</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>democratic9b1@naver.com</t>
-        </is>
-      </c>
+          <t>오니네일</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1483-9411</t>
+          <t>070-4798-7907</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 293 호텔더디자이너스 DDP점 1층</t>
+          <t>서울특별시 중구 만리재로33길 21 리가 아파트상가 103호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sHajSJei</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6176,7 +6124,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6192,22 +6140,22 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>182</v>
+        <v>117</v>
       </c>
       <c r="Q62" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="R62" t="n">
-        <v>243</v>
+        <v>121</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6216,17 +6164,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>2013893243</t>
+          <t>37002673</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013893243</t>
+          <t>https://m.place.naver.com/place/37002673</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6238,29 +6186,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>라라네일</t>
+          <t>동감 네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>redpepper30@naver.com</t>
+          <t>5nail@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>0507-1344-7250</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동9길 7 2층 라라네일</t>
+          <t>서울특별시 중구 소월로 10 단암빌딩 지하1층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lalanail_myeongdong</t>
+          <t>https://www.instagram.com/donggam_nail</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6295,13 +6239,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1002</v>
+        <v>30</v>
       </c>
       <c r="Q63" t="n">
-        <v>433</v>
+        <v>21</v>
       </c>
       <c r="R63" t="n">
-        <v>1435</v>
+        <v>51</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6310,17 +6254,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1303128966</t>
+          <t>37460311</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1303128966</t>
+          <t>https://m.place.naver.com/place/37460311</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6332,29 +6276,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>M네일</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>cjstkalswl0@naver.com</t>
-        </is>
-      </c>
+          <t>네일멜로디</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>02-318-2446</t>
+          <t>0507-1458-7441</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 102 소공지하쇼핑센터</t>
+          <t>서울특별시 중구 소공로 58 가-30</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/na.il_melody</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6364,7 +6304,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6385,17 +6325,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R64" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6404,17 +6344,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>37690803</t>
+          <t>2087273795</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37690803</t>
+          <t>https://m.place.naver.com/place/2087273795</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6426,25 +6366,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>꼬뇨네일</t>
+          <t>맥스네일</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>mono1584@naver.com</t>
+          <t>machojj@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>02-2272-4141</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로42가길 12 2층 꼬뇨네일</t>
+          <t>서울특별시 중구 퇴계로 204 3층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>http://instagram.com/kkonyo_nail</t>
+          <t>https://blog.naver.com/machojj</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6459,7 +6403,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6479,13 +6423,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>37</v>
+        <v>198</v>
       </c>
       <c r="Q65" t="n">
-        <v>18</v>
+        <v>532</v>
       </c>
       <c r="R65" t="n">
-        <v>55</v>
+        <v>730</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6494,17 +6438,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>35563100</t>
+          <t>32786203</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35563100</t>
+          <t>https://m.place.naver.com/place/32786203</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6516,29 +6460,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>마녀사냥 회현지하쇼핑센터점</t>
+          <t>바비 네일왁싱</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>geein0808@naver.com</t>
+          <t>uchka247@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>02-777-7748</t>
+          <t>0507-1490-9887</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 65-1</t>
+          <t>서울특별시 중구 을지로44길 6-9 4층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/barbie.waxnail</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6548,7 +6492,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6569,17 +6513,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>36</v>
+        <v>159</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R66" t="n">
-        <v>36</v>
+        <v>162</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6588,17 +6532,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>61218861</t>
+          <t>1019484164</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/61218861</t>
+          <t>https://m.place.naver.com/place/1019484164</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6610,24 +6554,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일 을지로지하쇼핑센터3구역점</t>
+          <t>RANSNAIL</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>skrud8631@naver.com</t>
+          <t>ransnail@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>02-2278-2990</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 131 을지로3구역지하쇼핑</t>
+          <t>서울특별시 중구 소공로 58</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6667,13 +6607,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6682,17 +6622,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>37588249</t>
+          <t>1077056709</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37588249</t>
+          <t>https://m.place.naver.com/place/1077056709</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6704,29 +6644,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>삼층네일</t>
+          <t>프로뷰티</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>wang8241@naver.com</t>
+          <t>probeauty_blog@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1327-8241</t>
+          <t>0507-1435-2789</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 중구 서소문로 139 동림빌딩 302</t>
+          <t>서울특별시 중구 명동8가길 9 3층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wang8241</t>
+          <t>https://blog.naver.com/probeauty_blog</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6757,17 +6697,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>531</v>
+        <v>572</v>
       </c>
       <c r="Q68" t="n">
-        <v>13</v>
+        <v>679</v>
       </c>
       <c r="R68" t="n">
-        <v>544</v>
+        <v>1251</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6776,17 +6716,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1894370134</t>
+          <t>19997455</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1894370134</t>
+          <t>https://m.place.naver.com/place/19997455</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6798,29 +6738,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>굿모닝네일</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>clsrn9606@naver.com</t>
-        </is>
-      </c>
+          <t>네일바이연</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1400-8607</t>
+          <t>0507-1317-9237</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 258 자산빌딩 3층</t>
+          <t>서울특별시 중구 소월로2길 30 남산트라팰리스 1층 108호(T타워 옆 건물)(안에있음</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gmnail_eyelash</t>
+          <t>http://instagram.com/_nailby_yeon</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6846,7 +6782,7 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6855,13 +6791,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>241</v>
+        <v>392</v>
       </c>
       <c r="Q69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R69" t="n">
-        <v>247</v>
+        <v>397</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6870,17 +6806,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>13051690</t>
+          <t>1319851472</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13051690</t>
+          <t>https://m.place.naver.com/place/1319851472</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6892,29 +6828,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>레푸스 청계천점</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>refuss_care@naver.com</t>
-        </is>
-      </c>
+          <t>마레네일 회현지하쇼핑센터점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>0507-1462-2414</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 중구 청계천로 400 롯데캐슬베네치아메가몰 2층 2103호</t>
+          <t>서울특별시 중구 소공로 58</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/refuss_care</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6924,12 +6852,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6940,22 +6868,22 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1073</v>
+        <v>3</v>
       </c>
       <c r="Q70" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>2023</v>
+        <v>3</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6964,17 +6892,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1308679538</t>
+          <t>37588265</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1308679538</t>
+          <t>https://m.place.naver.com/place/37588265</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6986,35 +6914,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>밀리미터네일</t>
+          <t>네일박스</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>zzan323@naver.com</t>
+          <t>smilehh406@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>070-8959-0722</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 중구 청구로3길 79 1층 102호</t>
+          <t>서울특별시 중구 퇴계로 439-6</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_eEUQxj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7030,22 +6962,22 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R71" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7054,17 +6986,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1846303126</t>
+          <t>1127129774</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1846303126</t>
+          <t>https://m.place.naver.com/place/1127129774</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7076,34 +7008,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>라무르네일</t>
+          <t>레푸스 청계천점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>mandumom82@naver.com</t>
+          <t>refuss_care@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>02-2274-2164</t>
+          <t>0507-1462-2414</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 248 104호(묵정동)</t>
+          <t>서울특별시 중구 청계천로 400 롯데캐슬베네치아메가몰 2층 2103호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_TGklxj</t>
+          <t>https://blog.naver.com/refuss_care</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7113,7 +7045,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7133,13 +7065,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>19</v>
+        <v>1074</v>
       </c>
       <c r="Q72" t="n">
-        <v>3</v>
+        <v>950</v>
       </c>
       <c r="R72" t="n">
-        <v>22</v>
+        <v>2024</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7148,17 +7080,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1185961653</t>
+          <t>1308679538</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185961653</t>
+          <t>https://m.place.naver.com/place/1308679538</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7170,29 +7102,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>생크추어리 미호즈네일</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>stmhu27@naver.com</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>ncontact.roamusic.yt@gmail.com</t>
-        </is>
-      </c>
+          <t>지아네일</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 중구 삼일대로 299 이화빌딩 별관</t>
+          <t>서울특별시 중구 명동10길 40 6층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCyzO0wKjVEHw9LMt3ud5Jqw</t>
+          <t>https://www.instagram.com/jeonjia9</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7227,13 +7151,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="Q73" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R73" t="n">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7242,17 +7166,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1692160158</t>
+          <t>1279897442</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1692160158</t>
+          <t>https://m.place.naver.com/place/1279897442</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7264,29 +7188,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>디디 네일바</t>
+          <t>드로잉쇼</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>heeja090@naver.com</t>
+          <t>odshow@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1476-0228</t>
+          <t>02-777-1090</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로16길 5-5 유일빌딩4층 503호</t>
+          <t>서울특별시 중구 남대문로 60</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/didi___nailbar</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7296,7 +7220,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7317,17 +7241,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>189</v>
+        <v>2</v>
       </c>
       <c r="Q74" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="R74" t="n">
-        <v>213</v>
+        <v>7</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7336,17 +7260,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1134899134</t>
+          <t>1726036993</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134899134</t>
+          <t>https://m.place.naver.com/place/1726036993</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7358,29 +7282,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>테라피 여유</t>
+          <t>네일리</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>suyom819@naver.com</t>
+          <t>ysbfly@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1368-6500</t>
+          <t>0507-1358-8653</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로83길 46 5층</t>
+          <t>서울특별시 중구 세종대로20길 23 2층 206호(노모어피자,반포식스건물 아님)</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gridau_nailsalon</t>
+          <t>https://www.instagram.com/nail_lee____</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7415,13 +7339,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="Q75" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="R75" t="n">
-        <v>51</v>
+        <v>126</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7430,17 +7354,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1353443114</t>
+          <t>2065943871</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1353443114</t>
+          <t>https://m.place.naver.com/place/2065943871</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7376,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>핑크레이디 회현지하쇼핑센터점</t>
+          <t>릴리엔젤네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>geein0808@naver.com</t>
+          <t>kiyu0987@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -7465,12 +7389,12 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동8나길 52-1</t>
+          <t>서울특별시 중구 남대문로 117 동아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/lilyangel_nail</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7480,7 +7404,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7501,17 +7425,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2</v>
+        <v>235</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="R76" t="n">
-        <v>2</v>
+        <v>287</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7520,17 +7444,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>37588413</t>
+          <t>1110775717</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37588413</t>
+          <t>https://m.place.naver.com/place/1110775717</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7542,12 +7466,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>네일링</t>
+          <t>유르네일</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>gulgomi@naver.com</t>
+          <t>sohee5369@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -7555,12 +7479,12 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로 32 남산타운2상가 106호</t>
+          <t>서울특별시 중구 퇴계로 414</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/yurr_nail</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7570,7 +7494,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7591,17 +7515,17 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="Q77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R77" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7610,17 +7534,17 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1720718118</t>
+          <t>1907754185</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1720718118</t>
+          <t>https://m.place.naver.com/place/1907754185</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7632,24 +7556,20 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>드로잉쇼</t>
+          <t>란스</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>odshow@naver.com</t>
+          <t>ypplove@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>02-777-1090</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 60</t>
+          <t>서울특별시 중구 회현동2가</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7689,13 +7609,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="Q78" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7704,17 +7624,17 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1726036993</t>
+          <t>1498975945</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726036993</t>
+          <t>https://m.place.naver.com/place/1498975945</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7726,29 +7646,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>네일온 명동본점</t>
+          <t>네일리앤래쉬</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>nailon_myeongdong@naver.com</t>
+          <t>dear_my_spring@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>0507-1302-8995</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 88 을특8호</t>
+          <t>서울특별시 중구 동호로 178 1층</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailon_myeongdong</t>
+          <t>https://www.instagram.com/nailee_lash</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7763,7 +7679,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7783,13 +7699,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>29</v>
+        <v>242</v>
       </c>
       <c r="Q79" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="R79" t="n">
-        <v>39</v>
+        <v>276</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7798,17 +7714,17 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>2054691209</t>
+          <t>1131170616</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2054691209</t>
+          <t>https://m.place.naver.com/place/1131170616</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7820,29 +7736,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>바이올렛네일</t>
+          <t>네일은</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>violet_nail@naver.com</t>
+          <t>sungunara226@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>02-2118-8867</t>
+          <t>0507-1470-4223</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 247 굿모닝시티 B2 6호</t>
+          <t>서울특별시 중구 다산로46길 17 이스트동(EAST) 1층</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/naileun_nail</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7852,7 +7768,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -7873,17 +7789,17 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R80" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7892,17 +7808,17 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>120895291</t>
+          <t>1988790934</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/120895291</t>
+          <t>https://m.place.naver.com/place/1988790934</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7914,24 +7830,24 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>코코네일</t>
+          <t>푸딩네일</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>jjuahlee@naver.com</t>
+          <t>hero_0304@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>02-318-6668</t>
+          <t>02-2233-2202</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로 70 덕제빌딩 302호</t>
+          <t>서울특별시 중구 다산로 32 남산타운스포츠상가 103호</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7971,13 +7887,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="Q81" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -7986,17 +7902,17 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1874418389</t>
+          <t>1937114523</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1874418389</t>
+          <t>https://m.place.naver.com/place/1937114523</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8008,29 +7924,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>호시탐탐네일</t>
+          <t>강앤니네일스</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>uvistavie@naver.com</t>
+          <t>beczzam@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>02-6361-8521</t>
+          <t>0507-1468-2316</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 78 하나허브빌딩 1층</t>
+          <t>서울특별시 중구 장충단로 227-2 4층</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/kangannynails</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8040,7 +7956,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -8061,17 +7977,17 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8080,17 +7996,17 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>19816425</t>
+          <t>1711237836</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19816425</t>
+          <t>https://m.place.naver.com/place/1711237836</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8102,29 +8018,33 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>리오풋케어</t>
+          <t>가디스네일</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>rio-footcare@naver.com</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>ara_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>arachonail@gmail.com</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0507-1448-3378</t>
+          <t>0507-1396-8776</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 중구 청계천로 400 롯데캐슬배네치아 메가몰동 1층 1122호 리오풋케어</t>
+          <t>서울특별시 중구 퇴계로18길 24 3층</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rio-footcare</t>
+          <t>https://youtube.com/@aranail</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8139,7 +8059,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8150,7 +8070,7 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8159,13 +8079,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>209</v>
+        <v>39</v>
       </c>
       <c r="Q83" t="n">
-        <v>677</v>
+        <v>5</v>
       </c>
       <c r="R83" t="n">
-        <v>886</v>
+        <v>44</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8174,17 +8094,17 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>38571388</t>
+          <t>19851675</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38571388</t>
+          <t>https://m.place.naver.com/place/19851675</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8196,25 +8116,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RANSNAIL</t>
+          <t>메이드인네일</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ransnail@naver.com</t>
+          <t>madeinnail4241@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1412-4241</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 58</t>
+          <t>서울특별시 중구 동호로11길 7 녹원빌딩 1층 3호 네일샵</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/madeinnail4241</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8224,12 +8148,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8245,17 +8169,17 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8264,17 +8188,17 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1077056709</t>
+          <t>38501356</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1077056709</t>
+          <t>https://m.place.naver.com/place/38501356</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8286,25 +8210,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>네일리앤래쉬</t>
+          <t>네일 괜찮아</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>dear_my_spring@naver.com</t>
+          <t>nobleliz_@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1423-7899</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 중구 동호로 178 1층</t>
+          <t>서울특별시 중구 다산로46길 17 지하1층B102호</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailee_lash</t>
+          <t>https://www.instagram.com/_nail_ok_</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8339,13 +8267,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>242</v>
+        <v>9</v>
       </c>
       <c r="Q85" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="R85" t="n">
-        <v>276</v>
+        <v>14</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8354,17 +8282,17 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1131170616</t>
+          <t>1040309489</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1131170616</t>
+          <t>https://m.place.naver.com/place/1040309489</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8376,24 +8304,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>네일박스</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>smilehh406@naver.com</t>
-        </is>
-      </c>
+          <t>호시탐탐네일</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>070-8959-0722</t>
+          <t>02-6361-8521</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 439-6</t>
+          <t>서울특별시 중구 남대문로 78 하나허브빌딩 1층</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8433,13 +8357,13 @@
         </is>
       </c>
       <c r="P86" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>5</v>
-      </c>
       <c r="R86" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8448,51 +8372,51 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1127129774</t>
+          <t>19816425</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1127129774</t>
+          <t>https://m.place.naver.com/place/19816425</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>네일아트재료</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>네일MOA</t>
+          <t>러빗네일</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>moa-nail-ks@naver.com</t>
+          <t>hyokyungsea@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>02-567-5253</t>
+          <t>0507-1340-3760</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문시장길 37</t>
+          <t>서울특별시 중구 청파로 464 103호 러빗네일</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>http://www.nailmoa.co.kr</t>
+          <t>https://www.instagram.com/luv.it_nail</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8507,7 +8431,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -8523,17 +8447,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>19</v>
+        <v>151</v>
       </c>
       <c r="Q87" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R87" t="n">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8542,17 +8466,17 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1179880730</t>
+          <t>1027224018</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1179880730</t>
+          <t>https://m.place.naver.com/place/1027224018</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8564,39 +8488,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>수네일</t>
+          <t>네일모노</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>yjh1000j@naver.com</t>
+          <t>ekgus9633@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>02-775-1447</t>
+          <t>0507-1335-5164</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 58</t>
+          <t>서울특별시 중구 다산로42나길 57 101호</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_gFskxj</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -8612,22 +8536,22 @@
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R88" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8636,17 +8560,17 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1253308517</t>
+          <t>1174841316</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1253308517</t>
+          <t>https://m.place.naver.com/place/1174841316</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8658,29 +8582,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>아이러브네일</t>
+          <t>지호네일</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>saddysad@naver.com</t>
+          <t>suk2time@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>02-2231-8000</t>
+          <t>0507-1314-5759</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 중구 청계천로 400</t>
+          <t>서울특별시 중구 다산로 265 5층,6층</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jihonail</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8690,7 +8614,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -8711,17 +8635,17 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R89" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8730,17 +8654,17 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1532896403</t>
+          <t>1285361463</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1532896403</t>
+          <t>https://m.place.naver.com/place/1285361463</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8752,29 +8676,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>지유네일</t>
+          <t>네일블룸 청구점</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>jiyunail@naver.com</t>
+          <t>oladeoro@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0507-1426-4142</t>
+          <t>02-2231-0522</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 중구 동호로10길 30 동아약수하이츠아파트상가 1층</t>
+          <t>서울특별시 중구 청구로4길 9</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jiyunail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8784,12 +8708,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -8805,17 +8729,17 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>495</v>
+        <v>2</v>
       </c>
       <c r="Q90" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>589</v>
+        <v>2</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8824,17 +8748,17 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>31234315</t>
+          <t>21888751</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31234315</t>
+          <t>https://m.place.naver.com/place/21888751</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8846,39 +8770,35 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>네일리듄</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>nail_lidune@naver.com</t>
-        </is>
-      </c>
+          <t>바이올렛네일</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0507-1373-9377</t>
+          <t>02-2118-8867</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 393-1 써니빌딩 601호</t>
+          <t>서울특별시 중구 장충단로 247 굿모닝시티 B2 6호</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_TURxjn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8894,22 +8814,22 @@
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>114</v>
+        <v>2</v>
       </c>
       <c r="Q91" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>123</v>
+        <v>2</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8918,17 +8838,17 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1983160367</t>
+          <t>120895291</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1983160367</t>
+          <t>https://m.place.naver.com/place/120895291</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8940,29 +8860,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>네일프렌즈</t>
+          <t>안젤라네일샵</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>friends41@naver.com</t>
+          <t>angella3977@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>02-753-4179</t>
+          <t>0507-1493-3335</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 103</t>
+          <t>서울특별시 중구 소공로 102 소공지하쇼핑센터 57호</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/friends41</t>
+          <t>https://blog.naver.com/angella3977</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8993,17 +8913,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1</v>
+        <v>666</v>
       </c>
       <c r="Q92" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="R92" t="n">
-        <v>10</v>
+        <v>678</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9012,17 +8932,17 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>36434848</t>
+          <t>1274163754</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36434848</t>
+          <t>https://m.place.naver.com/place/1274163754</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9034,39 +8954,35 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>묘나하우스</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>hanil36chin@naver.com</t>
-        </is>
-      </c>
+          <t>코코네일</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0507-1373-9597</t>
+          <t>02-318-6668</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>대구광역시 중구 태평로 176-7 1층 105호</t>
+          <t>서울특별시 중구 세종대로 70 덕제빌딩 302호</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_KXxlkxj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -9082,22 +8998,22 @@
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="Q93" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="R93" t="n">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9106,17 +9022,17 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>1843844140</t>
+          <t>1874418389</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1843844140</t>
+          <t>https://m.place.naver.com/place/1874418389</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9128,29 +9044,25 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>테리네일</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>terrywinner@naver.com</t>
-        </is>
-      </c>
+          <t>꽁냥네일</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0507-1400-7242</t>
+          <t>0507-1418-2440</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>서울특별시 중구 서소문로9길 28 덕수궁 롯데캐슬 상가 201동 130호</t>
+          <t>서울특별시 중구 장충단로 249-28 3층</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/terrywinner</t>
+          <t>https://www.instagram.com/ggongnyang_nail</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9165,7 +9077,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9185,13 +9097,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>158</v>
+        <v>277</v>
       </c>
       <c r="Q94" t="n">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="R94" t="n">
-        <v>286</v>
+        <v>319</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9200,17 +9112,17 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>31519898</t>
+          <t>1570914826</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31519898</t>
+          <t>https://m.place.naver.com/place/1570914826</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9222,25 +9134,25 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>마녀세상</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>punkwitch@naver.com</t>
-        </is>
-      </c>
+          <t>테라피 여유</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0507-1368-6500</t>
+        </is>
+      </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 65-1</t>
+          <t>서울특별시 중구 퇴계로83길 46 5층</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/gridau_nailsalon</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9250,7 +9162,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -9271,17 +9183,17 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="Q95" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R95" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9290,17 +9202,17 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>1874819639</t>
+          <t>1353443114</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1874819639</t>
+          <t>https://m.place.naver.com/place/1353443114</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9312,29 +9224,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>나비네일</t>
+          <t>알렌시아네일</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>jytgh@naver.com</t>
+          <t>mugununa@naver.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>02-319-7844</t>
+          <t>0507-1352-5127</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동7길 19 중원빌딩 505호</t>
+          <t>서울특별시 중구 동호로 172 1층 알렌시아네일</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>http://instagram.com/navinailnavinail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9344,7 +9256,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -9365,17 +9277,17 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>26</v>
+        <v>676</v>
       </c>
       <c r="Q96" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="R96" t="n">
-        <v>28</v>
+        <v>688</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9384,17 +9296,17 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>735546684</t>
+          <t>1517501228</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/735546684</t>
+          <t>https://m.place.naver.com/place/1517501228</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9406,29 +9318,25 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>크리스탈손톱</t>
+          <t>Nail the sharp</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>juyean123@naver.com</t>
+          <t>happyjoint-hospital@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>02-3398-4445</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 275</t>
+          <t>서울특별시 중구 다산로 32 남산타운2상가 407호</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nail_the_sharp/</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -9438,7 +9346,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -9459,17 +9367,17 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Q97" t="n">
         <v>1</v>
       </c>
       <c r="R97" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9478,17 +9386,17 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1895018257</t>
+          <t>1917957135</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895018257</t>
+          <t>https://m.place.naver.com/place/1917957135</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9500,34 +9408,30 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>강앤니네일스</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>beczzam@naver.com</t>
-        </is>
-      </c>
+          <t>네일드윌</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0507-1468-2316</t>
+          <t>0507-1349-8525</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 227-2 4층</t>
+          <t>서울특별시 중구 마장로18길 6 7층 701호</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>http://instagram.com/kangannynails</t>
+          <t>http://pf.kakao.com/_KDKmG/chat</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -9548,7 +9452,7 @@
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -9560,10 +9464,10 @@
         <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9572,51 +9476,51 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>1711237836</t>
+          <t>2058420406</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1711237836</t>
+          <t>https://m.place.naver.com/place/2058420406</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>네일아트,네일샵</t>
+          <t>네일아트재료</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>수야디나 네일&amp;래쉬</t>
+          <t>네일MOA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>vastron@naver.com</t>
+          <t>moa-nail-ks@naver.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0507-1305-2499</t>
+          <t>02-567-5253</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>서울특별시 중구 충무로 36 2층</t>
+          <t>서울특별시 중구 남대문시장길 37</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yun_ju423/</t>
+          <t>http://www.nailmoa.co.kr</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9631,7 +9535,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -9647,17 +9551,17 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>184</v>
+        <v>19</v>
       </c>
       <c r="Q99" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="R99" t="n">
-        <v>216</v>
+        <v>20</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9666,17 +9570,17 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>1324800762</t>
+          <t>1179880730</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324800762</t>
+          <t>https://m.place.naver.com/place/1179880730</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9688,44 +9592,40 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>오니네일</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>wjsska1907@naver.com</t>
-        </is>
-      </c>
+          <t>네일퐁당</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>070-4798-7907</t>
+          <t>0507-1342-2541</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>서울특별시 중구 만리재로33길 21 리가 아파트상가 103호</t>
+          <t>서울특별시 중구 동호로7길 14 2층</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/p/CVh14YJhw8l/?utm_medium=copy_link</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -9741,17 +9641,17 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>117</v>
+        <v>752</v>
       </c>
       <c r="Q100" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R100" t="n">
-        <v>120</v>
+        <v>761</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9760,17 +9660,17 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>37002673</t>
+          <t>1234653779</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37002673</t>
+          <t>https://m.place.naver.com/place/1234653779</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9782,20 +9682,20 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>아셀네일</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>asher9809@naver.com</t>
-        </is>
-      </c>
+          <t>손발공주</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>0507-1325-1832</t>
+        </is>
+      </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 253 10층 11호</t>
+          <t>서울특별시 중구 퇴계로80길 13-26 1층</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -9835,13 +9735,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="Q101" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="R101" t="n">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -9850,17 +9750,17 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>1229434440</t>
+          <t>1044748908</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1229434440</t>
+          <t>https://m.place.naver.com/place/1044748908</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9872,34 +9772,34 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>네일드윌</t>
+          <t>충무로 하트비트 네일스튜디오</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ramiu_s@naver.com</t>
+          <t>eunishero@naver.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>0507-1349-8525</t>
+          <t>0507-1310-9697</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>서울특별시 중구 마장로18길 6 7층 701호</t>
+          <t>서울특별시 중구 마른내로6길 38 2층</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_KDKmG/chat</t>
+          <t>https://www.instagram.com/heartbeatnailstudio</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -9920,7 +9820,7 @@
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -9944,17 +9844,17 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>2058420406</t>
+          <t>2098893814</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2058420406</t>
+          <t>https://m.place.naver.com/place/2098893814</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9966,25 +9866,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>더나은네일</t>
+          <t>굿모닝네일</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>merryyear09@naver.com</t>
+          <t>clsrn9606@naver.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0507-1400-8607</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로20길 37</t>
+          <t>서울특별시 중구 을지로 258 자산빌딩 3층</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thebetternail</t>
+          <t>https://www.instagram.com/gmnail_eyelash</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -10010,7 +9914,7 @@
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -10019,13 +9923,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="Q103" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="R103" t="n">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -10034,17 +9938,17 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>67963615</t>
+          <t>13051690</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/67963615</t>
+          <t>https://m.place.naver.com/place/13051690</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10056,29 +9960,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>네일바이연</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>twinkle_gy@naver.com</t>
-        </is>
-      </c>
+          <t>꼬뇨네일</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>0507-1317-9237</t>
-        </is>
-      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소월로2길 30 남산트라팰리스 1층 108호(T타워 옆 건물)(안에있음</t>
+          <t>서울특별시 중구 다산로42가길 12 2층 꼬뇨네일</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>http://instagram.com/_nailby_yeon</t>
+          <t>http://instagram.com/kkonyo_nail</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -10113,13 +10009,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>392</v>
+        <v>37</v>
       </c>
       <c r="Q104" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="R104" t="n">
-        <v>397</v>
+        <v>55</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -10128,17 +10024,17 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>1319851472</t>
+          <t>35563100</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1319851472</t>
+          <t>https://m.place.naver.com/place/35563100</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10150,12 +10046,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>유르네일</t>
+          <t>더나은네일</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>sohee5369@naver.com</t>
+          <t>merryyear09@naver.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -10163,12 +10059,12 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>서울특별시 중구 퇴계로 414</t>
+          <t>서울특별시 중구 퇴계로20길 37</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>http://instagram.com/yurr_nail</t>
+          <t>https://www.instagram.com/thebetternail</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10203,13 +10099,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>80</v>
+        <v>220</v>
       </c>
       <c r="Q105" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="R105" t="n">
-        <v>86</v>
+        <v>249</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -10218,17 +10114,17 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>1907754185</t>
+          <t>67963615</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1907754185</t>
+          <t>https://m.place.naver.com/place/67963615</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10240,29 +10136,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>엘로아네일</t>
+          <t>네일블라썸</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>hhhong88@naver.com</t>
+          <t>wilklove@naver.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0507-1314-9339</t>
+          <t>0507-1347-8173</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 12 시청광장지하쇼핑센터(시티스타몰) 607호 엘로아 네일</t>
+          <t>서울특별시 중구 소공로 102 95호</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/eloa__nail/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -10272,7 +10168,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -10293,17 +10189,17 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>11</v>
+        <v>334</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R106" t="n">
-        <v>11</v>
+        <v>344</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -10312,17 +10208,17 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>2087274322</t>
+          <t>1794862527</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2087274322</t>
+          <t>https://m.place.naver.com/place/1794862527</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10334,34 +10230,30 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>네일퐁당</t>
+          <t>리라뷰티</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>skan612@naver.com</t>
+          <t>rira_225@naver.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>0507-1342-2541</t>
-        </is>
-      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>서울특별시 중구 동호로7길 14 2층</t>
+          <t>서울특별시 중구 퇴계로18길 6 (남산동1가) 2층 리라뷰티</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/CVh14YJhw8l/?utm_medium=copy_link</t>
+          <t>https://www.instagram.com/lira_4994/</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -10371,7 +10263,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -10391,13 +10283,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>751</v>
+        <v>121</v>
       </c>
       <c r="Q107" t="n">
-        <v>9</v>
+        <v>277</v>
       </c>
       <c r="R107" t="n">
-        <v>760</v>
+        <v>398</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -10406,17 +10298,17 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>1234653779</t>
+          <t>1100664846</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1234653779</t>
+          <t>https://m.place.naver.com/place/1100664846</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10428,35 +10320,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>손톱공주 회현지하쇼핑센터점</t>
+          <t>아머네일</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>skrud8631@naver.com</t>
+          <t>dntndus111@naver.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>0507-1364-4429</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>서울특별시 중구 소공로 58</t>
+          <t>서울특별시 중구 마른내로 74 1층 아머네일</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_pzkMG</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -10472,22 +10368,22 @@
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>359</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -10496,17 +10392,17 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>37586344</t>
+          <t>1312237193</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37586344</t>
+          <t>https://m.place.naver.com/place/1312237193</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10518,29 +10414,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>네일바이안</t>
+          <t>나비네일</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ye1yang@naver.com</t>
+          <t>052young@naver.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>02-511-5621</t>
+          <t>02-319-7844</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로9길 12 8층</t>
+          <t>서울특별시 중구 명동7길 19 중원빌딩 505호</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailbyahn</t>
+          <t>http://instagram.com/navinailnavinail</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -10575,13 +10471,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="Q109" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="R109" t="n">
-        <v>102</v>
+        <v>28</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -10590,17 +10486,17 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>1084164588</t>
+          <t>735546684</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1084164588</t>
+          <t>https://m.place.naver.com/place/735546684</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10612,34 +10508,34 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GK네일 현대시티아울렛 동대문점</t>
+          <t>안온네일</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>liziah@naver.com</t>
+          <t>didakf032@naver.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0507-1339-5357</t>
+          <t>0507-1407-4494</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로13길 20 지하1층</t>
+          <t>서울특별시 중구 서애로1길 11 헤센스마트상가 1층 121호 안온네일</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gknaildongdaemun?igsh=MTM5OTg0OHRzdXVjZg%3D%3D&amp;utm_source=qr</t>
+          <t>http://pf.kakao.com/_zuYRG/chat</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -10660,7 +10556,7 @@
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -10669,13 +10565,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>332</v>
+        <v>109</v>
       </c>
       <c r="Q110" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="R110" t="n">
-        <v>378</v>
+        <v>112</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -10684,17 +10580,17 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>1245812382</t>
+          <t>1306558328</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245812382</t>
+          <t>https://m.place.naver.com/place/1306558328</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10706,24 +10602,20 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>빨간고양이네일 을지로입구지하쇼핑센터점</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>skrud8631@naver.com</t>
-        </is>
-      </c>
+          <t>마녀사냥 회현지하쇼핑센터점</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>02-756-4143</t>
+          <t>02-777-7748</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 58 을지로입구지하쇼핑센터 8</t>
+          <t>서울특별시 중구 소공로 65-1</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -10763,13 +10655,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -10778,17 +10670,17 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>31315234</t>
+          <t>61218861</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31315234</t>
+          <t>https://m.place.naver.com/place/61218861</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10800,25 +10692,25 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>센스네일</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>nail_hy-@naver.com</t>
-        </is>
-      </c>
+          <t>더샵 네일</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>0507-1305-9365</t>
+        </is>
+      </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>서울특별시 중구 청계천로 400 롯데캐슬베네치아메가몰 1007호 1층 센스네일</t>
+          <t>서울특별시 중구 소공로 58 회현지하쇼핑센터 다-5호</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>http://instagram.com/sense.nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10828,7 +10720,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -10849,17 +10741,17 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P112" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q112" t="n">
-        <v>283</v>
+        <v>2</v>
       </c>
       <c r="R112" t="n">
-        <v>303</v>
+        <v>23</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -10868,17 +10760,17 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>185384764</t>
+          <t>230882348</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/185384764</t>
+          <t>https://m.place.naver.com/place/230882348</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10890,34 +10782,30 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>읍내쌀롱</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>hot1god@naver.com</t>
-        </is>
-      </c>
+          <t>라무르네일</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>0507-1332-6517</t>
+          <t>02-2274-2164</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>대구광역시 중구 태평로 176-7 102호</t>
+          <t>서울특별시 중구 퇴계로 248 104호(묵정동)</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>http://instagram.com/eupnae_nail</t>
+          <t>http://pf.kakao.com/_TGklxj</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -10938,7 +10826,7 @@
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -10947,13 +10835,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q113" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="R113" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -10962,17 +10850,17 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>1400699570</t>
+          <t>1185961653</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1400699570</t>
+          <t>https://m.place.naver.com/place/1185961653</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10984,29 +10872,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>알렌시아네일</t>
+          <t>수야디나 네일&amp;래쉬</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>mugununa@naver.com</t>
+          <t>vastron@naver.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>0507-1352-5127</t>
+          <t>0507-1305-2499</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>서울특별시 중구 동호로 172 1층 알렌시아네일</t>
+          <t>서울특별시 중구 충무로 36 2층</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/yun_ju423/</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -11016,7 +10904,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -11037,17 +10925,17 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P114" t="n">
-        <v>674</v>
+        <v>185</v>
       </c>
       <c r="Q114" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="R114" t="n">
-        <v>686</v>
+        <v>217</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -11056,17 +10944,17 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>1517501228</t>
+          <t>1324800762</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1517501228</t>
+          <t>https://m.place.naver.com/place/1324800762</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -11078,29 +10966,29 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>9층네일 명동점</t>
+          <t>리오풋케어</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>dmgktnqls@naver.com</t>
+          <t>rio-footcare@naver.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>0507-1359-1372</t>
+          <t>0507-1448-3378</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동10길 25-1 303호</t>
+          <t>서울특별시 중구 청계천로 400 롯데캐슬배네치아 메가몰동 1층 1122호 리오풋케어</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/9.nailstudio</t>
+          <t>https://blog.naver.com/rio-footcare</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -11115,7 +11003,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -11135,13 +11023,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>258</v>
+        <v>209</v>
       </c>
       <c r="Q115" t="n">
-        <v>23</v>
+        <v>678</v>
       </c>
       <c r="R115" t="n">
-        <v>281</v>
+        <v>887</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -11150,17 +11038,17 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>1681308543</t>
+          <t>38571388</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1681308543</t>
+          <t>https://m.place.naver.com/place/38571388</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -11172,29 +11060,29 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>네일아토</t>
+          <t>네일도사랑해 본점</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>sk3374@naver.com</t>
+          <t>nesanail@naver.com</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>0507-1416-6630</t>
+          <t>0507-1442-9779</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>서울특별시 중구 남대문로 29-1 3층 301호(남대문로3가)</t>
+          <t>서울특별시 중구 명동2길 57 태평양빌딩 8층</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ato</t>
+          <t>https://www.instagram.com/nail.lovu</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -11229,13 +11117,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="Q116" t="n">
-        <v>22</v>
+        <v>169</v>
       </c>
       <c r="R116" t="n">
-        <v>214</v>
+        <v>344</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -11244,17 +11132,17 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>1446399532</t>
+          <t>37294039</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446399532</t>
+          <t>https://m.place.naver.com/place/37294039</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -11266,29 +11154,25 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>러빗네일</t>
+          <t>니꼬네일</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>hyokyungsea@naver.com</t>
+          <t>hahere@naver.com</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>0507-1340-3760</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>서울특별시 중구 청파로 464 103호 러빗네일</t>
+          <t>서울특별시 중구 동호로10길 16 1층 102호</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luv.it_nail</t>
+          <t>https://www.instagram.com/nail_nikko</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -11323,13 +11207,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>151</v>
+        <v>243</v>
       </c>
       <c r="Q117" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>158</v>
+        <v>243</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -11338,17 +11222,17 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>1027224018</t>
+          <t>1827341634</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027224018</t>
+          <t>https://m.place.naver.com/place/1827341634</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -11360,24 +11244,24 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>헤이뷰티 스튜디오</t>
+          <t>네일인</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>gemma0321@naver.com</t>
+          <t>mneilacademy@naver.com</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>0507-1404-0899</t>
+          <t>0507-1344-4179</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다산로 32 5상가동 1층 102호</t>
+          <t>서울특별시 중구 소공로 46</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -11417,13 +11301,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R118" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -11432,17 +11316,17 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>1656356418</t>
+          <t>1071509328</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1656356418</t>
+          <t>https://m.place.naver.com/place/1071509328</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -11454,29 +11338,29 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>프로뷰티</t>
+          <t>네일하트</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>probeauty_blog@naver.com</t>
+          <t>nailheart053@naver.com</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>0507-1435-2789</t>
+          <t>0507-1484-8604</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동8가길 9 3층</t>
+          <t>서울특별시 중구 명동길 47 양원빌딩3층</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/probeauty_blog</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -11486,12 +11370,12 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -11507,17 +11391,17 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P119" t="n">
-        <v>571</v>
+        <v>373</v>
       </c>
       <c r="Q119" t="n">
-        <v>679</v>
+        <v>9</v>
       </c>
       <c r="R119" t="n">
-        <v>1250</v>
+        <v>382</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -11526,17 +11410,17 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>19997455</t>
+          <t>1101101042</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19997455</t>
+          <t>https://m.place.naver.com/place/1101101042</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -11548,24 +11432,24 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>엔79 Nail</t>
+          <t>크리스탈손톱</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>loveucream@naver.com</t>
+          <t>juyean123@naver.com</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>0507-1390-0326</t>
+          <t>02-3398-4445</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동길 36-1 삼호빌딩 7층 701호</t>
+          <t>서울특별시 중구 장충단로 275</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -11605,13 +11489,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>163</v>
+        <v>3</v>
       </c>
       <c r="Q120" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="R120" t="n">
-        <v>182</v>
+        <v>4</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -11620,17 +11504,17 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>1756267523</t>
+          <t>1895018257</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756267523</t>
+          <t>https://m.place.naver.com/place/1895018257</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -11642,29 +11526,25 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>네일도사랑해 본점</t>
+          <t>손톱공주 회현지하쇼핑센터점</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>nesanail@naver.com</t>
+          <t>skrud8631@naver.com</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>0507-1442-9779</t>
-        </is>
-      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동2길 57 태평양빌딩 8층</t>
+          <t>서울특별시 중구 소공로 58</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.lovu</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -11674,7 +11554,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -11695,17 +11575,17 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P121" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -11714,17 +11594,17 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>37294039</t>
+          <t>37586344</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37294039</t>
+          <t>https://m.place.naver.com/place/37586344</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -11736,29 +11616,25 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>명동네일 제니뷰티</t>
+          <t>깜네일 회현지하쇼핑센터점</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>hyoyeol@naver.com</t>
+          <t>skrud8631@naver.com</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>0507-1487-9603</t>
-        </is>
-      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>서울특별시 중구 명동8길 43 3층</t>
+          <t>서울특별시 중구 명동8나길 52-1</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jennybeauty.md/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -11768,7 +11644,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -11789,17 +11665,17 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P122" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -11808,17 +11684,17 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>1845062262</t>
+          <t>61704046</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845062262</t>
+          <t>https://m.place.naver.com/place/61704046</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
